--- a/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
+++ b/InputData/trans/BAADTbVT/cn - BAU Avg Annual Dist Traveled by Veh Type.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\EPS Models\EPS China 3.3.1\InputData\trans\BAADTbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zhlxl\Desktop\EPS\eps-china2019-smart-trans\InputData\trans\BAADTbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB38108-3D81-42D7-AA91-FFF4A0C6FCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4D882F-3644-4D7F-9413-561014E2F146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9768" yWindow="475" windowWidth="13218" windowHeight="13314" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About " sheetId="32" r:id="rId1"/>
     <sheet name="LDVs HDVs" sheetId="24" r:id="rId2"/>
     <sheet name="rail" sheetId="25" r:id="rId3"/>
     <sheet name="aircraft" sheetId="26" r:id="rId4"/>
-    <sheet name="motorbikes" sheetId="27" r:id="rId5"/>
-    <sheet name="ships" sheetId="33" r:id="rId6"/>
+    <sheet name="ships" sheetId="33" r:id="rId5"/>
+    <sheet name="motorbikes" sheetId="27" r:id="rId6"/>
     <sheet name="China Vehicle Fleet Model Data" sheetId="34" r:id="rId7"/>
     <sheet name="converter" sheetId="29" r:id="rId8"/>
     <sheet name="raw data" sheetId="35" r:id="rId9"/>
@@ -28,7 +28,6 @@
   <externalReferences>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="ab">'[1]1997  Table 1a Modified'!#REF!</definedName>
@@ -38,7 +37,7 @@
     <definedName name="Eno_TM" localSheetId="9">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="7">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_TM" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Eno_TM" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="2">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM" localSheetId="8">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_TM">'[2]1997  Table 1a Modified'!#REF!</definedName>
@@ -48,7 +47,7 @@
     <definedName name="Eno_Tons" localSheetId="9">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="7">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Eno_Tons" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Eno_Tons" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="2">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons" localSheetId="8">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Eno_Tons">'[2]1997  Table 1a Modified'!#REF!</definedName>
@@ -60,7 +59,7 @@
     <definedName name="Sum_T2" localSheetId="9">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="7">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_T2" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Sum_T2" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="2">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2" localSheetId="8">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_T2">'[2]1997  Table 1a Modified'!#REF!</definedName>
@@ -70,7 +69,7 @@
     <definedName name="Sum_TTM" localSheetId="9">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="7">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="1">'[1]1997  Table 1a Modified'!#REF!</definedName>
-    <definedName name="Sum_TTM" localSheetId="4">'[1]1997  Table 1a Modified'!#REF!</definedName>
+    <definedName name="Sum_TTM" localSheetId="5">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="2">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM" localSheetId="8">'[1]1997  Table 1a Modified'!#REF!</definedName>
     <definedName name="Sum_TTM">'[2]1997  Table 1a Modified'!#REF!</definedName>
@@ -80,7 +79,7 @@
     <definedName name="ti_tbl_50" localSheetId="9">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="7">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="1">#REF!</definedName>
-    <definedName name="ti_tbl_50" localSheetId="4">#REF!</definedName>
+    <definedName name="ti_tbl_50" localSheetId="5">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="2">#REF!</definedName>
     <definedName name="ti_tbl_50" localSheetId="8">#REF!</definedName>
     <definedName name="ti_tbl_50">#REF!</definedName>
@@ -90,7 +89,7 @@
     <definedName name="ti_tbl_69" localSheetId="9">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="7">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="1">#REF!</definedName>
-    <definedName name="ti_tbl_69" localSheetId="4">#REF!</definedName>
+    <definedName name="ti_tbl_69" localSheetId="5">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="2">#REF!</definedName>
     <definedName name="ti_tbl_69" localSheetId="8">#REF!</definedName>
     <definedName name="ti_tbl_69">#REF!</definedName>
@@ -112,7 +111,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -134,7 +133,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="175">
   <si>
     <t>Source:</t>
   </si>
@@ -575,10 +574,6 @@
   </si>
   <si>
     <t>1990</t>
-    <phoneticPr fontId="50" type="noConversion"/>
-  </si>
-  <si>
-    <t>Covid Impact</t>
     <phoneticPr fontId="50" type="noConversion"/>
   </si>
   <si>
@@ -675,12 +670,200 @@
     </r>
     <phoneticPr fontId="42" type="noConversion"/>
   </si>
+  <si>
+    <t>HDV-psgr</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDV-psgr</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>LDV-frgt</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>HDV-frgt</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>私家车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>营运车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算周转量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>年报公里</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>年鉴周转量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>汽油保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销汽油</t>
+  </si>
+  <si>
+    <t>柴油保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销柴油</t>
+  </si>
+  <si>
+    <t>天然气保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销天然气</t>
+  </si>
+  <si>
+    <t>插电保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销插电</t>
+  </si>
+  <si>
+    <t>纯电保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销纯电</t>
+  </si>
+  <si>
+    <t>燃料电池保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销燃料电池</t>
+  </si>
+  <si>
+    <t>甲醇保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销甲醇</t>
+  </si>
+  <si>
+    <t>LPG保有量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020新销LPG</t>
+  </si>
+  <si>
+    <t>出租车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型公交车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型公交车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>大型公交车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型客车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>大型客车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>微轻型货车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型货车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>重型货车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>年报数据</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞机架次</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>周转量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>客运</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>货运</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>民航行业发展统计公报</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>BCD</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>客运数量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>机车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>客车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>货车</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>货运数量</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>船舶总数</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
+  <si>
+    <t>《交通运输行业发展统计公报》</t>
+    <phoneticPr fontId="42" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="176" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="###0.00_)"/>
@@ -689,8 +872,9 @@
     <numFmt numFmtId="181" formatCode="0.0"/>
     <numFmt numFmtId="182" formatCode="0.000_ "/>
     <numFmt numFmtId="183" formatCode="0_ "/>
+    <numFmt numFmtId="188" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1035,8 +1219,22 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1212,8 +1410,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -1428,6 +1638,15 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1688,7 +1907,7 @@
       <alignment horizontal="left"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1768,34 +1987,55 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="183" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="180" fontId="45" fillId="32" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="182" fontId="51" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="188" fontId="57" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="154">
     <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1970,14 +2210,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>590550</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>103038</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>57989</xdr:colOff>
+      <xdr:colOff>359913</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>73139</xdr:rowOff>
     </xdr:to>
@@ -2018,99 +2258,388 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>879895</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>39019</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>603849</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>68654</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="组合 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EFF1236-6683-4DEE-A722-8F43C330A308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="879895" y="2997879"/>
+          <a:ext cx="4399471" cy="849145"/>
+          <a:chOff x="1932317" y="2208362"/>
+          <a:chExt cx="3873260" cy="849145"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="图片 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE36B97B-5DB9-E366-D0D8-C059D1322280}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1932317" y="2208362"/>
+            <a:ext cx="3838755" cy="739676"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="5" name="图片 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0749AB2-8696-238D-FB75-FE25752AAE64}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1992703" y="2734574"/>
+            <a:ext cx="3812874" cy="322933"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>646981</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>8626</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1114303</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>30390</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="6" name="组合 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E6BB617-0290-4A8E-802D-CB1CD8DAA4C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5322498" y="2967486"/>
+          <a:ext cx="4978937" cy="841274"/>
+          <a:chOff x="5848710" y="2255608"/>
+          <a:chExt cx="5177344" cy="841274"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="图片 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DE96378-4985-C235-00D5-87111F030032}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5865961" y="2255608"/>
+            <a:ext cx="5088903" cy="576432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="8" name="图片 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D8AAD678-52FB-16B5-511B-DF44750F3007}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5848710" y="2818335"/>
+            <a:ext cx="5177344" cy="278547"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>384809</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1078302</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>133909</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1494794</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>82840</xdr:rowOff>
+      <xdr:colOff>129396</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>163545</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="组合 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19EFA43D-415C-6874-A2E0-A775568A9A6F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC33D643-CA62-4480-A294-FA1724EDF57D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2213609" y="2333625"/>
-          <a:ext cx="4739010" cy="3902365"/>
+          <a:off x="4641011" y="1609026"/>
+          <a:ext cx="3873260" cy="849145"/>
+          <a:chOff x="1932317" y="2208362"/>
+          <a:chExt cx="3873260" cy="849145"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="图片 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D1256E74-2AA0-CFC5-378D-154DAA29FD77}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1932317" y="2208362"/>
+            <a:ext cx="3838755" cy="739676"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="图片 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{853715B9-D0EC-8BD5-AAA1-7718B893CB20}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1992703" y="2734574"/>
+            <a:ext cx="3812874" cy="322933"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>163829</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>10839</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>138024</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>69011</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>568776</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>113085</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>346552</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>90776</xdr:rowOff>
     </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="组合 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAB2F576-A720-8B70-44D8-9F19BA957515}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EC98A9C-91E5-4BDE-8F7E-F59A9F6FC0C5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7669529" y="2725464"/>
-          <a:ext cx="5281747" cy="3359796"/>
+          <a:off x="8522899" y="1544128"/>
+          <a:ext cx="5177344" cy="841274"/>
+          <a:chOff x="5848710" y="2255608"/>
+          <a:chExt cx="5177344" cy="841274"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="图片 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EB62BEB-72C0-C654-08A2-3F3BFF234314}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5865961" y="2255608"/>
+            <a:ext cx="5088903" cy="576432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="图片 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D18676A-8449-E9E0-3EF7-034DF5D0635C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5848710" y="2818335"/>
+            <a:ext cx="5177344" cy="278547"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>12</xdr:col>
@@ -2138,7 +2667,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2182,7 +2711,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2197,6 +2726,383 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>77637</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>8627</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>293297</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>38262</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="8" name="组合 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A91D10CF-93E2-AA7C-988D-228EC8811B7E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1940943" y="2303253"/>
+          <a:ext cx="3873260" cy="849145"/>
+          <a:chOff x="1932317" y="2208362"/>
+          <a:chExt cx="3873260" cy="849145"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="图片 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C599BFC7-4973-D702-D772-DF1E14E3840F}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1932317" y="2208362"/>
+            <a:ext cx="3838755" cy="739676"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="图片 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{623F5C72-3A75-2D7B-AF9B-EF5F4DF95E3E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1992703" y="2734574"/>
+            <a:ext cx="3812874" cy="322933"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>327804</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>124883</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>337926</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>146648</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="11" name="组合 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D566F1BA-E402-A40E-D690-AC55974E2EE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5848710" y="2255608"/>
+          <a:ext cx="5177344" cy="841274"/>
+          <a:chOff x="5848710" y="2255608"/>
+          <a:chExt cx="5177344" cy="841274"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="图片 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE4C5F02-B2B8-C8B3-FAF3-2844F461AF98}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5865961" y="2255608"/>
+            <a:ext cx="5088903" cy="576432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="10" name="图片 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B994A889-EE9A-FB02-6532-39E61ECE10A0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5848710" y="2818335"/>
+            <a:ext cx="5177344" cy="278547"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>60385</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>90777</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>370936</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>120413</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="组合 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F47C50DA-968F-4CB4-903E-C564C88B87F8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="60385" y="582483"/>
+          <a:ext cx="3873260" cy="849145"/>
+          <a:chOff x="1932317" y="2208362"/>
+          <a:chExt cx="3873260" cy="849145"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="3" name="图片 2">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6982616-25F2-5A14-C7E1-425BCC4F30AE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1932317" y="2208362"/>
+            <a:ext cx="3838755" cy="739676"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="图片 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{013845AE-7D3A-BC8C-EDD6-8FBA41498DF0}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1992703" y="2734574"/>
+            <a:ext cx="3812874" cy="322933"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>405443</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>43132</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>372432</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>64897</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="5" name="组合 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A05228B0-C5CC-4EB3-AC95-DA0D3C3AA26C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="3968152" y="534838"/>
+          <a:ext cx="5177344" cy="841274"/>
+          <a:chOff x="5848710" y="2255608"/>
+          <a:chExt cx="5177344" cy="841274"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="6" name="图片 5">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF48742B-957B-9F4F-E98D-31A920B44548}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5865961" y="2255608"/>
+            <a:ext cx="5088903" cy="576432"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="7" name="图片 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C6D232C-DCE8-9546-7E73-505AC259EB29}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5848710" y="2818335"/>
+            <a:ext cx="5177344" cy="278547"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2286,6 +3192,9 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Rail shipments 93-97"/>
       <sheetName val="Waterborne Flows 93-97"/>
@@ -2364,34 +3273,10 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="About "/>
-      <sheetName val="passenger"/>
-      <sheetName val="freight"/>
-      <sheetName val="BCDTRtSY-psgr"/>
-      <sheetName val="BCDTRtSY-frgt"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2429,9 +3314,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2464,26 +3349,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2516,26 +3384,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2711,7 +3562,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:B45"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="51.5" customWidth="1"/>
   </cols>
@@ -2902,1008 +3753,1039 @@
   <sheetPr codeName="Sheet8">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AS7"/>
-  <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AQ7"/>
+  <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45" ht="54">
+    <row r="1" spans="1:43" ht="51.65">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="5">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C1" s="5">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D1" s="5">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="E1" s="5">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F1" s="5">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="G1" s="5">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H1" s="5">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="I1" s="5">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="J1" s="5">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="K1" s="5">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="L1" s="5">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="M1" s="5">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="N1" s="5">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="O1" s="5">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="P1" s="5">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="Q1" s="5">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="R1" s="5">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="S1" s="5">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="T1" s="5">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="U1" s="5">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="V1" s="5">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="W1" s="5">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="X1" s="5">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="Y1" s="5">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="Z1" s="5">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="AA1" s="5">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="AB1" s="5">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="AC1" s="5">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="AD1" s="5">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="AE1" s="5">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="AF1" s="5">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="AG1" s="5">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="AH1" s="5">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="AI1" s="5">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="5">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="5">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="5">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="5">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="5">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="5">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="5">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="AQ1" s="5">
-        <v>2058</v>
-      </c>
-      <c r="AR1" s="5">
-        <v>2059</v>
-      </c>
-      <c r="AS1" s="5">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:45" s="6" customFormat="1">
+    <row r="2" spans="1:43" s="6" customFormat="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>6214</v>
-      </c>
-      <c r="C2" s="6">
-        <v>6214</v>
-      </c>
-      <c r="D2" s="45">
-        <f>$B2*'raw data'!S$21</f>
-        <v>6214</v>
-      </c>
-      <c r="E2" s="45">
-        <f>$B2*'raw data'!T$21</f>
-        <v>3492.7246719160107</v>
-      </c>
-      <c r="F2" s="45">
-        <f>$B2*'raw data'!U$21</f>
-        <v>4042.6999673615924</v>
-      </c>
-      <c r="G2" s="45">
-        <f>$B2*'raw data'!V$21</f>
-        <v>2779.2128309738482</v>
-      </c>
-      <c r="H2" s="45">
-        <f>$B2*'raw data'!W$21</f>
-        <v>5698.7819246460767</v>
+      <c r="B2" s="38">
+        <f>'LDVs HDVs'!B23</f>
+        <v>11352.903703490325</v>
+      </c>
+      <c r="C2" s="38">
+        <f>$B2*'raw data'!T$22</f>
+        <v>9876.7937868592198</v>
+      </c>
+      <c r="D2" s="38">
+        <f>$B2*'raw data'!U$22</f>
+        <v>10225.790534907886</v>
+      </c>
+      <c r="E2" s="38">
+        <f>$B2*'raw data'!V$22</f>
+        <v>8949.5093804790322</v>
+      </c>
+      <c r="F2" s="38">
+        <f>$B2*'raw data'!W$22</f>
+        <v>9102.4916173008914</v>
+      </c>
+      <c r="G2" s="6">
+        <f>F2</f>
+        <v>9102.4916173008914</v>
+      </c>
+      <c r="H2" s="6">
+        <f>G2</f>
+        <v>9102.4916173008914</v>
       </c>
       <c r="I2" s="6">
-        <v>6214</v>
+        <f t="shared" ref="I2:AQ2" si="0">H2</f>
+        <v>9102.4916173008914</v>
       </c>
       <c r="J2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="K2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="L2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="M2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="N2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="O2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="P2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="Q2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="R2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="S2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="T2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="U2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="V2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="W2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="X2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="Y2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="Z2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AA2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AB2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AC2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AD2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AE2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AF2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AG2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AH2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AI2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AJ2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AK2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AL2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AM2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AN2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AO2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AP2" s="6">
-        <v>6214</v>
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
       </c>
       <c r="AQ2" s="6">
-        <v>6214</v>
-      </c>
-      <c r="AR2" s="6">
-        <v>6214</v>
-      </c>
-      <c r="AS2" s="6">
-        <v>6214</v>
-      </c>
-    </row>
-    <row r="3" spans="1:45">
+        <f t="shared" si="0"/>
+        <v>9102.4916173008914</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
-        <v>37283</v>
-      </c>
-      <c r="C3" s="6">
-        <v>37283</v>
-      </c>
-      <c r="D3" s="45">
-        <f>$B3*'raw data'!S$21</f>
-        <v>37283</v>
-      </c>
-      <c r="E3" s="45">
-        <f>$B3*'raw data'!T$21</f>
-        <v>20955.78595800525</v>
-      </c>
-      <c r="F3" s="45">
-        <f>$B3*'raw data'!U$21</f>
-        <v>24255.549224837825</v>
-      </c>
-      <c r="G3" s="45">
-        <f>$B3*'raw data'!V$21</f>
-        <v>16674.8297356289</v>
-      </c>
-      <c r="H3" s="45">
-        <f>$B3*'raw data'!W$21</f>
-        <v>34191.774460344335</v>
+      <c r="B3" s="38">
+        <f>'LDVs HDVs'!D23</f>
+        <v>31069.409059839683</v>
+      </c>
+      <c r="C3" s="38">
+        <f>$B3*'raw data'!T$22</f>
+        <v>27029.749778399819</v>
+      </c>
+      <c r="D3" s="38">
+        <f>$B3*'raw data'!U$22</f>
+        <v>27984.846642503784</v>
+      </c>
+      <c r="E3" s="38">
+        <f>$B3*'raw data'!V$22</f>
+        <v>24492.057282357662</v>
+      </c>
+      <c r="F3" s="38">
+        <f>$B3*'raw data'!W$22</f>
+        <v>24910.722658092891</v>
+      </c>
+      <c r="G3" s="6">
+        <f>F3</f>
+        <v>24910.722658092891</v>
+      </c>
+      <c r="H3" s="6">
+        <f t="shared" ref="H3:AQ3" si="1">G3</f>
+        <v>24910.722658092891</v>
       </c>
       <c r="I3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="J3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="K3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="L3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="M3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="N3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="O3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="P3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="Q3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="R3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="S3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="T3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="U3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="V3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="W3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="X3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="Y3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="Z3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AA3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AB3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AC3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AD3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AE3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AF3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AG3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AH3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AI3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AJ3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AK3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AL3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AM3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AN3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AO3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AP3" s="6">
-        <v>37283</v>
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
       </c>
       <c r="AQ3" s="6">
-        <v>37283</v>
-      </c>
-      <c r="AR3" s="6">
-        <v>37283</v>
-      </c>
-      <c r="AS3" s="6">
-        <v>37283</v>
-      </c>
-    </row>
-    <row r="4" spans="1:45">
+        <f t="shared" si="1"/>
+        <v>24910.722658092891</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <f>aircraft!G12</f>
-        <v>1140737.9853349791</v>
-      </c>
-      <c r="C4" s="6">
-        <f t="shared" ref="C4:AS4" si="0">$B$4</f>
-        <v>1140737.9853349791</v>
-      </c>
-      <c r="D4" s="45">
-        <f>$B$4*'raw data'!S24</f>
-        <v>1140737.9853349791</v>
-      </c>
-      <c r="E4" s="45">
-        <f>$B$4*'raw data'!T24</f>
-        <v>615075.20927501237</v>
-      </c>
-      <c r="F4" s="45">
-        <f>$B$4*'raw data'!U24</f>
-        <v>636359.70714322024</v>
-      </c>
-      <c r="G4" s="45">
-        <f>$B$4*'raw data'!V24</f>
-        <v>381415.47301650629</v>
-      </c>
-      <c r="H4" s="45">
-        <f>$B$4*'raw data'!W24</f>
-        <v>1026839.6084872081</v>
+      <c r="B4" s="38">
+        <f>aircraft!E27</f>
+        <v>832489.27135522617</v>
+      </c>
+      <c r="C4" s="38">
+        <f>aircraft!F27</f>
+        <v>832466.83716849552</v>
+      </c>
+      <c r="D4" s="38">
+        <f>aircraft!G27</f>
+        <v>830227.05473397288</v>
+      </c>
+      <c r="E4" s="38">
+        <f>aircraft!H27</f>
+        <v>486781.18511336844</v>
+      </c>
+      <c r="F4" s="38">
+        <f>aircraft!I27</f>
+        <v>1259470.6699362323</v>
+      </c>
+      <c r="G4" s="38">
+        <f>B4</f>
+        <v>832489.27135522617</v>
+      </c>
+      <c r="H4" s="6">
+        <f t="shared" ref="H4:AQ6" si="2">$B4</f>
+        <v>832489.27135522617</v>
       </c>
       <c r="I4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="J4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="K4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="L4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="M4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="N4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="O4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="P4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="Q4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="R4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="S4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="T4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="U4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="V4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="W4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="X4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="Y4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="Z4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AA4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AB4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AC4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AD4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AE4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AF4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AG4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AH4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AI4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AJ4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AK4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AL4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AM4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AN4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AO4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AP4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
       </c>
       <c r="AQ4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
-      </c>
-      <c r="AR4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
-      </c>
-      <c r="AS4" s="6">
-        <f t="shared" si="0"/>
-        <v>1140737.9853349791</v>
-      </c>
-    </row>
-    <row r="5" spans="1:45">
+        <f t="shared" si="2"/>
+        <v>832489.27135522617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
-        <f>rail!$E$8</f>
-        <v>137860.50569468629</v>
-      </c>
-      <c r="C5" s="6">
-        <f t="shared" ref="C5:AS5" si="1">$B$5</f>
-        <v>137860.50569468629</v>
-      </c>
-      <c r="D5" s="45">
-        <f>$B5*'raw data'!S21</f>
-        <v>137860.50569468629</v>
-      </c>
-      <c r="E5" s="45">
-        <f>$B5*'raw data'!T21</f>
-        <v>77487.735681147169</v>
-      </c>
-      <c r="F5" s="45">
-        <f>$B5*'raw data'!U21</f>
-        <v>89689.195666617466</v>
-      </c>
-      <c r="G5" s="45">
-        <f>$B5*'raw data'!V21</f>
-        <v>61658.140700227777</v>
-      </c>
-      <c r="H5" s="45">
-        <f>$B5*'raw data'!W21</f>
-        <v>126430.15094551751</v>
+      <c r="B5" s="38">
+        <f>rail!D25</f>
+        <v>16430.842393390882</v>
+      </c>
+      <c r="C5" s="38">
+        <f>rail!E25</f>
+        <v>16430.860300226996</v>
+      </c>
+      <c r="D5" s="38">
+        <f>rail!F25</f>
+        <v>18548.431401273247</v>
+      </c>
+      <c r="E5" s="38">
+        <f>rail!G25</f>
+        <v>12923.217202246135</v>
+      </c>
+      <c r="F5" s="38">
+        <f>rail!H25</f>
+        <v>28566.832019599085</v>
+      </c>
+      <c r="G5" s="38">
+        <f>rail!I25</f>
+        <v>29512.097226889557</v>
+      </c>
+      <c r="H5" s="6">
+        <f>G5</f>
+        <v>29512.097226889557</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" ref="I5:AQ5" si="3">H5</f>
+        <v>29512.097226889557</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="O5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="P5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="R5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="U5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="W5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="X5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="Y5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="Z5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AA5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AB5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AC5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AD5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AE5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AF5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AG5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AH5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AI5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AJ5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AK5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AL5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AM5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AN5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AO5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AP5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
       </c>
       <c r="AQ5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
-      </c>
-      <c r="AR5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
-      </c>
-      <c r="AS5" s="6">
-        <f t="shared" si="1"/>
-        <v>137860.50569468629</v>
-      </c>
-    </row>
-    <row r="6" spans="1:45">
+        <f t="shared" si="3"/>
+        <v>29512.097226889557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43">
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
-        <f>ships!J14</f>
-        <v>47850.236079851777</v>
-      </c>
-      <c r="C6" s="6">
-        <f t="shared" ref="C6:AS6" si="2">$B$6</f>
-        <v>47850.236079851777</v>
-      </c>
-      <c r="D6" s="45">
-        <f>$B$6*'raw data'!S23</f>
-        <v>47850.236079851777</v>
-      </c>
-      <c r="E6" s="45">
-        <f>$B$6*'raw data'!T23</f>
-        <v>19683.033519629804</v>
-      </c>
-      <c r="F6" s="45">
-        <f>$B$6*'raw data'!U23</f>
-        <v>19754.629882841549</v>
-      </c>
-      <c r="G6" s="45">
-        <f>$B$6*'raw data'!V23</f>
-        <v>13485.35400184082</v>
-      </c>
-      <c r="H6" s="45">
-        <f>$B$6*'raw data'!W23</f>
-        <v>42695.503768150134</v>
+      <c r="B6" s="38">
+        <f>ships!D25</f>
+        <v>48562.432819545516</v>
+      </c>
+      <c r="C6" s="38">
+        <f>ships!E25</f>
+        <v>20718.787113966806</v>
+      </c>
+      <c r="D6" s="38">
+        <f>ships!F25</f>
+        <v>20939.711526266026</v>
+      </c>
+      <c r="E6" s="38">
+        <f>ships!G25</f>
+        <v>14767.467510285478</v>
+      </c>
+      <c r="F6" s="38">
+        <f>ships!H25</f>
+        <v>36236.600356332157</v>
+      </c>
+      <c r="G6" s="38">
+        <f>ships!I25</f>
+        <v>39545.748292294891</v>
+      </c>
+      <c r="H6" s="6">
+        <f>$G6</f>
+        <v>39545.748292294891</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" ref="I6:AQ6" si="4">$G6</f>
+        <v>39545.748292294891</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="O6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="P6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="R6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="S6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="W6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="Y6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AK6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AL6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AM6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AN6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AP6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
       </c>
       <c r="AQ6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
-      </c>
-      <c r="AR6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
-      </c>
-      <c r="AS6" s="6">
-        <f t="shared" si="2"/>
-        <v>47850.236079851777</v>
-      </c>
-    </row>
-    <row r="7" spans="1:45">
+        <f t="shared" si="4"/>
+        <v>39545.748292294891</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="38">
         <f>motorbikes!$B$3</f>
         <v>3728.3290871807621</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="38">
+        <f>motorbikes!$B$3*'raw data'!T$21</f>
+        <v>2095.594944933754</v>
+      </c>
+      <c r="D7" s="38">
+        <f>motorbikes!$B$3*'raw data'!U$21</f>
+        <v>2425.5738460024049</v>
+      </c>
+      <c r="E7" s="38">
+        <f>motorbikes!$B$3*'raw data'!V$21</f>
+        <v>1667.495982810716</v>
+      </c>
+      <c r="F7" s="38">
+        <f>motorbikes!$B$3*'raw data'!W$21</f>
+        <v>3419.2041215252552</v>
+      </c>
+      <c r="G7" s="6">
         <f>motorbikes!$B$3</f>
         <v>3728.3290871807621</v>
       </c>
-      <c r="D7" s="45">
-        <f>motorbikes!$B$3*'raw data'!S$21</f>
+      <c r="H7" s="6">
+        <f>motorbikes!$B$3</f>
         <v>3728.3290871807621</v>
-      </c>
-      <c r="E7" s="45">
-        <f>motorbikes!$B$3*'raw data'!T$21</f>
-        <v>2095.594944933754</v>
-      </c>
-      <c r="F7" s="45">
-        <f>motorbikes!$B$3*'raw data'!U$21</f>
-        <v>2425.5738460024049</v>
-      </c>
-      <c r="G7" s="45">
-        <f>motorbikes!$B$3*'raw data'!V$21</f>
-        <v>1667.495982810716</v>
-      </c>
-      <c r="H7" s="45">
-        <f>motorbikes!$B$3*'raw data'!W$21</f>
-        <v>3419.2041215252552</v>
       </c>
       <c r="I7" s="6">
         <f>motorbikes!$B$3</f>
@@ -4042,14 +4924,6 @@
         <v>3728.3290871807621</v>
       </c>
       <c r="AQ7" s="6">
-        <f>motorbikes!$B$3</f>
-        <v>3728.3290871807621</v>
-      </c>
-      <c r="AR7" s="6">
-        <f>motorbikes!$B$3</f>
-        <v>3728.3290871807621</v>
-      </c>
-      <c r="AS7" s="6">
         <f>motorbikes!$B$3</f>
         <v>3728.3290871807621</v>
       </c>
@@ -4066,989 +4940,1009 @@
   <sheetPr codeName="Sheet9">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AT7"/>
-  <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="13.5"/>
+  <dimension ref="A1:AQ7"/>
+  <sheetFormatPr defaultColWidth="9.375" defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="54">
+    <row r="1" spans="1:43">
       <c r="A1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="5">
-        <v>2016</v>
-      </c>
-      <c r="C1" s="1">
-        <v>2017</v>
-      </c>
-      <c r="D1" s="5">
-        <v>2018</v>
-      </c>
-      <c r="E1" s="1">
+        <v>92</v>
+      </c>
+      <c r="B1" s="1">
         <v>2019</v>
       </c>
-      <c r="F1" s="5">
+      <c r="C1" s="5">
         <v>2020</v>
       </c>
-      <c r="G1" s="1">
+      <c r="D1" s="1">
         <v>2021</v>
       </c>
-      <c r="H1" s="5">
+      <c r="E1" s="5">
         <v>2022</v>
       </c>
-      <c r="I1" s="1">
+      <c r="F1" s="1">
         <v>2023</v>
       </c>
-      <c r="J1" s="5">
+      <c r="G1" s="5">
         <v>2024</v>
       </c>
-      <c r="K1" s="1">
+      <c r="H1" s="1">
         <v>2025</v>
       </c>
-      <c r="L1" s="5">
+      <c r="I1" s="5">
         <v>2026</v>
       </c>
-      <c r="M1" s="1">
+      <c r="J1" s="1">
         <v>2027</v>
       </c>
-      <c r="N1" s="5">
+      <c r="K1" s="5">
         <v>2028</v>
       </c>
-      <c r="O1" s="1">
+      <c r="L1" s="1">
         <v>2029</v>
       </c>
-      <c r="P1" s="5">
+      <c r="M1" s="5">
         <v>2030</v>
       </c>
-      <c r="Q1" s="1">
+      <c r="N1" s="1">
         <v>2031</v>
       </c>
-      <c r="R1" s="5">
+      <c r="O1" s="5">
         <v>2032</v>
       </c>
-      <c r="S1" s="1">
+      <c r="P1" s="1">
         <v>2033</v>
       </c>
-      <c r="T1" s="5">
+      <c r="Q1" s="5">
         <v>2034</v>
       </c>
-      <c r="U1" s="1">
+      <c r="R1" s="1">
         <v>2035</v>
       </c>
-      <c r="V1" s="5">
+      <c r="S1" s="5">
         <v>2036</v>
       </c>
-      <c r="W1" s="1">
+      <c r="T1" s="1">
         <v>2037</v>
       </c>
-      <c r="X1" s="5">
+      <c r="U1" s="5">
         <v>2038</v>
       </c>
-      <c r="Y1" s="1">
+      <c r="V1" s="1">
         <v>2039</v>
       </c>
-      <c r="Z1" s="5">
+      <c r="W1" s="5">
         <v>2040</v>
       </c>
-      <c r="AA1" s="1">
+      <c r="X1" s="1">
         <v>2041</v>
       </c>
-      <c r="AB1" s="5">
+      <c r="Y1" s="5">
         <v>2042</v>
       </c>
-      <c r="AC1" s="1">
+      <c r="Z1" s="1">
         <v>2043</v>
       </c>
-      <c r="AD1" s="5">
+      <c r="AA1" s="5">
         <v>2044</v>
       </c>
-      <c r="AE1" s="1">
+      <c r="AB1" s="1">
         <v>2045</v>
       </c>
-      <c r="AF1" s="5">
+      <c r="AC1" s="5">
         <v>2046</v>
       </c>
+      <c r="AD1" s="1">
+        <v>2047</v>
+      </c>
+      <c r="AE1" s="5">
+        <v>2048</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>2049</v>
+      </c>
       <c r="AG1" s="1">
-        <v>2047</v>
-      </c>
-      <c r="AH1" s="5">
-        <v>2048</v>
+        <v>2050</v>
+      </c>
+      <c r="AH1" s="1">
+        <v>2051</v>
       </c>
       <c r="AI1" s="1">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="AJ1" s="1">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="AK1" s="1">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="AL1" s="1">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="AM1" s="1">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="AN1" s="1">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="AO1" s="1">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="AP1" s="1">
-        <v>2056</v>
-      </c>
-      <c r="AQ1" s="1">
-        <v>2057</v>
-      </c>
-      <c r="AR1" s="1">
-        <v>2058</v>
-      </c>
-      <c r="AS1" s="1">
         <v>2059</v>
       </c>
-      <c r="AT1" s="5">
+      <c r="AQ1" s="5">
         <v>2060</v>
       </c>
     </row>
-    <row r="2" spans="1:46">
+    <row r="2" spans="1:43">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="6">
-        <v>18642</v>
+        <f>'LDVs HDVs'!E23</f>
+        <v>15534.704529919842</v>
       </c>
       <c r="C2" s="6">
-        <v>18642</v>
+        <f>B2</f>
+        <v>15534.704529919842</v>
       </c>
       <c r="D2" s="6">
-        <v>18642</v>
+        <f t="shared" ref="D2:AQ2" si="0">C2</f>
+        <v>15534.704529919842</v>
       </c>
       <c r="E2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="F2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="G2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="H2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="I2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="J2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="K2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="L2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="M2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="N2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="O2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="P2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="Q2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="R2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="S2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="T2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="U2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="V2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="W2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="X2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="Y2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="Z2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AA2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AB2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AC2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AD2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AE2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AF2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AG2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AH2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AI2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AJ2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AK2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AL2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AM2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AN2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AO2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AP2" s="6">
-        <v>18642</v>
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
       </c>
       <c r="AQ2" s="6">
-        <v>18642</v>
-      </c>
-      <c r="AR2" s="6">
-        <v>18642</v>
-      </c>
-      <c r="AS2" s="6">
-        <v>18642</v>
-      </c>
-      <c r="AT2" s="6">
-        <v>18642</v>
-      </c>
-    </row>
-    <row r="3" spans="1:46">
+        <f t="shared" si="0"/>
+        <v>15534.704529919842</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="6">
-        <v>46604</v>
+        <f>'LDVs HDVs'!F23</f>
+        <v>36306.934435591582</v>
       </c>
       <c r="C3" s="6">
-        <v>46604</v>
+        <f>B3</f>
+        <v>36306.934435591582</v>
       </c>
       <c r="D3" s="6">
-        <v>46604</v>
+        <f t="shared" ref="D3:AQ3" si="1">C3</f>
+        <v>36306.934435591582</v>
       </c>
       <c r="E3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="F3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="G3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="H3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="I3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="J3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="K3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="L3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="M3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="N3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="O3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="P3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="Q3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="R3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="S3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="T3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="U3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="V3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="W3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="X3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="Y3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="Z3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AA3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AB3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AC3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AD3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AE3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AF3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AG3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AH3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AI3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AJ3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AK3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AL3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AM3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AN3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AO3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AP3" s="6">
-        <v>46604</v>
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
       </c>
       <c r="AQ3" s="6">
-        <v>46604</v>
-      </c>
-      <c r="AR3" s="6">
-        <v>46604</v>
-      </c>
-      <c r="AS3" s="6">
-        <v>46604</v>
-      </c>
-      <c r="AT3" s="6">
-        <v>46604</v>
-      </c>
-    </row>
-    <row r="4" spans="1:46">
+        <f t="shared" si="1"/>
+        <v>36306.934435591582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
-        <f>aircraft!H12</f>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="C4">
-        <f t="shared" ref="C4:L7" si="0">$B4</f>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+      <c r="B4" s="52">
+        <f>aircraft!E32</f>
+        <v>3203383.8434537211</v>
+      </c>
+      <c r="C4" s="52">
+        <f>aircraft!F32</f>
+        <v>3203297.8908665339</v>
+      </c>
+      <c r="D4" s="52">
+        <f>aircraft!G32</f>
+        <v>3484710.9203222673</v>
+      </c>
+      <c r="E4" s="52">
+        <f>aircraft!H32</f>
+        <v>2826422.4300539652</v>
+      </c>
+      <c r="F4" s="52">
+        <f>aircraft!I32</f>
+        <v>2737417.24134245</v>
+      </c>
+      <c r="G4" s="52">
+        <f>aircraft!J32</f>
+        <v>3275448.4268608387</v>
       </c>
       <c r="H4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" ref="D4:AQ7" si="2">$B4</f>
+        <v>3203383.8434537211</v>
       </c>
       <c r="I4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="J4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="K4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="L4">
-        <f t="shared" si="0"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4:V7" si="1">$B4</f>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="N4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="O4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="P4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="R4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="S4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="T4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="U4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="V4">
-        <f t="shared" si="1"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="W4">
-        <f t="shared" ref="W4:AF7" si="2">$B4</f>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="X4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="Y4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="Z4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AA4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AB4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AC4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AD4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AE4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AF4">
         <f t="shared" si="2"/>
-        <v>4771235.4266679734</v>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AG4">
-        <f t="shared" ref="AG4:AT7" si="3">$B4</f>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AH4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AK4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AL4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AM4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AN4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AO4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AP4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
       </c>
       <c r="AQ4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="AR4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="AS4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
-      </c>
-      <c r="AT4">
-        <f t="shared" si="3"/>
-        <v>4771235.4266679734</v>
-      </c>
-    </row>
-    <row r="5" spans="1:46">
+        <f t="shared" si="2"/>
+        <v>3203383.8434537211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="6">
-        <f>rail!F8</f>
-        <v>91606.044987982794</v>
+        <f>rail!D30</f>
+        <v>522.14192500125102</v>
       </c>
       <c r="C5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>rail!E30</f>
+        <v>522.46559899225224</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>rail!F30</f>
+        <v>537.80613637083309</v>
       </c>
       <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>rail!G30</f>
+        <v>563.80716782872753</v>
       </c>
       <c r="F5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>rail!H30</f>
+        <v>566.16351581496099</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>rail!I30</f>
+        <v>550.41485804107867</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f>G5</f>
+        <v>550.41485804107867</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f t="shared" ref="I5:AQ5" si="3">H5</f>
+        <v>550.41485804107867</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="L5" s="6">
-        <f t="shared" si="0"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="M5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="N5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="O5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="P5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="Q5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="R5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="S5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="T5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="U5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="V5" s="6">
-        <f t="shared" si="1"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="W5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="X5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="Y5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="Z5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AA5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AB5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AC5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AD5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AE5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AF5" s="6">
-        <f t="shared" si="2"/>
-        <v>91606.044987982794</v>
+        <f t="shared" si="3"/>
+        <v>550.41485804107867</v>
       </c>
       <c r="AG5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AH5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AI5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AJ5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AK5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AL5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AM5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AN5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AO5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AP5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
+        <v>550.41485804107867</v>
       </c>
       <c r="AQ5" s="6">
         <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
-      </c>
-      <c r="AR5" s="6">
-        <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
-      </c>
-      <c r="AS5" s="6">
-        <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
-      </c>
-      <c r="AT5" s="6">
-        <f t="shared" si="3"/>
-        <v>91606.044987982794</v>
-      </c>
-    </row>
-    <row r="6" spans="1:46">
+        <v>550.41485804107867</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <f>ships!J15</f>
-        <v>22614.358312312637</v>
+        <f>ships!D30</f>
+        <v>22769.886012460112</v>
       </c>
       <c r="C6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>ships!E30</f>
+        <v>22769.630777300627</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>ships!F30</f>
+        <v>25055.019492774827</v>
       </c>
       <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>ships!G30</f>
+        <v>27093.981489833517</v>
       </c>
       <c r="F6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>ships!H30</f>
+        <v>29993.366585977961</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>ships!I30</f>
+        <v>35035.712842952897</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f>$G6</f>
+        <v>35035.712842952897</v>
       </c>
       <c r="I6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f t="shared" ref="I6:AQ6" si="4">$G6</f>
+        <v>35035.712842952897</v>
       </c>
       <c r="J6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="K6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="L6" s="6">
-        <f t="shared" si="0"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="M6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="N6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="O6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="P6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="Q6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="R6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="S6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="T6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="U6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="V6" s="6">
-        <f t="shared" si="1"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="W6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="X6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="Y6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="Z6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AA6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AB6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AC6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AE6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AF6" s="6">
-        <f t="shared" si="2"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AG6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AH6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AI6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AJ6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AK6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AL6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AM6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AN6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AO6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AP6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
       </c>
       <c r="AQ6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
-      </c>
-      <c r="AR6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
-      </c>
-      <c r="AS6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
-      </c>
-      <c r="AT6" s="6">
-        <f t="shared" si="3"/>
-        <v>22614.358312312637</v>
-      </c>
-    </row>
-    <row r="7" spans="1:46">
+        <f t="shared" si="4"/>
+        <v>35035.712842952897</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -5057,83 +5951,83 @@
         <v>3728.3290871807621</v>
       </c>
       <c r="C7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C6:R7" si="5">$B7</f>
         <v>3728.3290871807621</v>
       </c>
       <c r="D7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="E7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="F7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="G7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="H7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="J7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="K7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="L7" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="M7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="N7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="O7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="P7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="Q7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="R7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="S7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="T7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="U7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="V7" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="W7" s="6">
@@ -5177,59 +6071,47 @@
         <v>3728.3290871807621</v>
       </c>
       <c r="AG7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AH7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AI7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AJ7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AK7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AL7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AM7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AN7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AO7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AP7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
       <c r="AQ7" s="6">
-        <f t="shared" si="3"/>
-        <v>3728.3290871807621</v>
-      </c>
-      <c r="AR7" s="6">
-        <f t="shared" si="3"/>
-        <v>3728.3290871807621</v>
-      </c>
-      <c r="AS7" s="6">
-        <f t="shared" si="3"/>
-        <v>3728.3290871807621</v>
-      </c>
-      <c r="AT7" s="6">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3728.3290871807621</v>
       </c>
     </row>
@@ -5243,109 +6125,848 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:X26"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-    <col min="4" max="4" width="31.125" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="25.625" customWidth="1"/>
-    <col min="7" max="7" width="25.375" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="26.25" customWidth="1"/>
+    <col min="4" max="4" width="11.5" customWidth="1"/>
+    <col min="5" max="5" width="28.25" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+    <col min="7" max="7" width="25.625" customWidth="1"/>
+    <col min="8" max="8" width="25.375" customWidth="1"/>
+    <col min="9" max="9" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:24">
       <c r="A1" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="9"/>
+      <c r="F1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="81">
+    <row r="2" spans="1:24" ht="90.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>10000</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>30000</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>60000</v>
       </c>
-      <c r="C3">
-        <f>B3*50%</f>
+      <c r="D3">
+        <f>C3*50%</f>
         <v>30000</v>
       </c>
-      <c r="D3" s="18"/>
-      <c r="E3">
+      <c r="E3" s="18"/>
+      <c r="F3">
         <v>75000</v>
       </c>
-      <c r="F3">
-        <f>E3*80%</f>
+      <c r="G3">
+        <f>F3*80%</f>
         <v>60000</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:24">
       <c r="A4" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="18"/>
-    </row>
-    <row r="5" spans="1:8" ht="65.25" customHeight="1">
+      <c r="B4" s="9"/>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:24" ht="65.25" customHeight="1">
       <c r="A5" t="s">
         <v>1</v>
       </c>
-      <c r="B5">
-        <f>'LDVs HDVs'!B2/converter!D2</f>
+      <c r="C5">
+        <f>'LDVs HDVs'!C2/converter!D2</f>
         <v>6213.8818119679363</v>
       </c>
-      <c r="E5">
-        <f>E2/converter!D2</f>
+      <c r="F5">
+        <f>F2/converter!D2</f>
         <v>18641.645435903811</v>
       </c>
-      <c r="F5" s="18"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
-        <f>B3/converter!D2</f>
+      <c r="C6">
+        <f>C3/converter!D2</f>
         <v>37283.290871807621</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6">
-        <f>E3/converter!D2</f>
+      <c r="E6" s="18"/>
+      <c r="F6">
+        <f>F3/converter!D2</f>
         <v>46604.113589759523</v>
       </c>
-      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="B15" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="44"/>
+      <c r="D15" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="E15" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="25.85">
+      <c r="B16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="H16">
+        <v>2019</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="L16" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="M16" s="40" t="s">
+        <v>139</v>
+      </c>
+      <c r="N16" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="O16" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="P16" s="41" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q16" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="R16" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="S16" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="T16" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="U16" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="V16" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="W16" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="X16" s="41" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>2858281</v>
+      </c>
+      <c r="C17">
+        <v>219557919</v>
+      </c>
+      <c r="D17">
+        <v>2310494</v>
+      </c>
+      <c r="E17">
+        <v>18926340</v>
+      </c>
+      <c r="F17">
+        <v>8502856</v>
+      </c>
+      <c r="H17" t="s">
+        <v>151</v>
+      </c>
+      <c r="I17" s="6">
+        <v>1849624.4879981384</v>
+      </c>
+      <c r="J17" s="42">
+        <v>252202.2260543342</v>
+      </c>
+      <c r="K17" s="6">
+        <v>37143.237186500715</v>
+      </c>
+      <c r="L17" s="42">
+        <v>12686.579375605608</v>
+      </c>
+      <c r="M17" s="6">
+        <v>438244.30732902896</v>
+      </c>
+      <c r="N17" s="42">
+        <v>101792.34308760613</v>
+      </c>
+      <c r="O17" s="6">
+        <v>81082.727127729158</v>
+      </c>
+      <c r="P17" s="42">
+        <v>45907.413598834231</v>
+      </c>
+      <c r="Q17" s="6">
+        <v>432005.81981867674</v>
+      </c>
+      <c r="R17" s="42">
+        <v>252409.47100517977</v>
+      </c>
+      <c r="S17" s="6">
+        <v>0</v>
+      </c>
+      <c r="T17" s="42">
+        <v>0</v>
+      </c>
+      <c r="U17" s="6">
+        <v>17170.509876207107</v>
+      </c>
+      <c r="V17" s="42">
+        <v>15441.34302992158</v>
+      </c>
+      <c r="W17" s="6">
+        <v>3009.8343630489308</v>
+      </c>
+      <c r="X17" s="42">
+        <v>214.68451318357486</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18">
+        <v>1.67</v>
+      </c>
+      <c r="C18">
+        <v>1.67</v>
+      </c>
+      <c r="D18">
+        <v>21.19613726</v>
+      </c>
+      <c r="E18">
+        <v>1.25</v>
+      </c>
+      <c r="F18">
+        <v>10.82</v>
+      </c>
+      <c r="H18" t="s">
+        <v>130</v>
+      </c>
+      <c r="I18" s="6">
+        <v>215027955.77954271</v>
+      </c>
+      <c r="J18" s="42">
+        <v>21292753.300209127</v>
+      </c>
+      <c r="K18" s="6">
+        <v>2160864.4227178507</v>
+      </c>
+      <c r="L18" s="42">
+        <v>155130.81666752725</v>
+      </c>
+      <c r="M18" s="6">
+        <v>334141.89022303506</v>
+      </c>
+      <c r="N18" s="42">
+        <v>11971.318596533596</v>
+      </c>
+      <c r="O18" s="6">
+        <v>1038136.0203040794</v>
+      </c>
+      <c r="P18" s="42">
+        <v>567728.94393548486</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>994327.85989400966</v>
+      </c>
+      <c r="R18" s="42">
+        <v>403462.34471683868</v>
+      </c>
+      <c r="S18" s="6">
+        <v>0</v>
+      </c>
+      <c r="T18" s="42">
+        <v>0</v>
+      </c>
+      <c r="U18" s="6">
+        <v>257.26006564958482</v>
+      </c>
+      <c r="V18" s="42">
+        <v>0</v>
+      </c>
+      <c r="W18" s="6">
+        <v>534.30936711836864</v>
+      </c>
+      <c r="X18" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="44">
+        <v>8857.1</v>
+      </c>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44">
+        <v>59636.4</v>
+      </c>
+      <c r="F19" s="44"/>
+      <c r="H19" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="6">
+        <v>674.87458352262399</v>
+      </c>
+      <c r="J19" s="42">
+        <v>315.65000205703831</v>
+      </c>
+      <c r="K19" s="6">
+        <v>600.47896014217724</v>
+      </c>
+      <c r="L19" s="42">
+        <v>5.3139730986033378</v>
+      </c>
+      <c r="M19" s="6">
+        <v>365.60134918390975</v>
+      </c>
+      <c r="N19" s="42">
+        <v>179.61229073279281</v>
+      </c>
+      <c r="O19" s="6">
+        <v>0</v>
+      </c>
+      <c r="P19" s="42">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="6">
+        <v>60.579293324078058</v>
+      </c>
+      <c r="R19" s="42">
+        <v>46.762963267709374</v>
+      </c>
+      <c r="S19" s="6">
+        <v>0</v>
+      </c>
+      <c r="T19" s="42">
+        <v>0</v>
+      </c>
+      <c r="U19" s="6">
+        <v>0</v>
+      </c>
+      <c r="V19" s="42">
+        <v>0</v>
+      </c>
+      <c r="W19" s="6">
+        <v>0</v>
+      </c>
+      <c r="X19" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="C20" s="39">
+        <f>(44400*1702+96000*2858281)/(1702+2858281)</f>
+        <v>95969.292404884924</v>
+      </c>
+      <c r="D20" s="39">
+        <v>50000</v>
+      </c>
+      <c r="E20" s="39">
+        <v>25000</v>
+      </c>
+      <c r="F20" s="39">
+        <f>(48000*1113343+60000*7389513)/(1113343+7389513)</f>
+        <v>58428.749587197526</v>
+      </c>
+      <c r="H20" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="6">
+        <v>5348.972563276594</v>
+      </c>
+      <c r="J20" s="42">
+        <v>159.1577173076825</v>
+      </c>
+      <c r="K20" s="6">
+        <v>24952.351769303768</v>
+      </c>
+      <c r="L20" s="42">
+        <v>951.65338555697065</v>
+      </c>
+      <c r="M20" s="6">
+        <v>6649.6752874807589</v>
+      </c>
+      <c r="N20" s="42">
+        <v>60.370168633948545</v>
+      </c>
+      <c r="O20" s="6">
+        <v>0</v>
+      </c>
+      <c r="P20" s="42">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>1280.9452144694174</v>
+      </c>
+      <c r="R20" s="42">
+        <v>1212.8915698275118</v>
+      </c>
+      <c r="S20" s="6">
+        <v>0</v>
+      </c>
+      <c r="T20" s="42">
+        <v>0</v>
+      </c>
+      <c r="U20" s="6">
+        <v>0</v>
+      </c>
+      <c r="V20" s="42">
+        <v>0</v>
+      </c>
+      <c r="W20" s="6">
+        <v>0</v>
+      </c>
+      <c r="X20" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" s="44">
+        <f>(C17*C18*C20+D17*D18*D20)/10^8</f>
+        <v>376369.43672413111</v>
+      </c>
+      <c r="D21" s="44"/>
+      <c r="E21" s="44">
+        <f>(E17*E18*E20+F17*F18*F20)/10^8</f>
+        <v>59669.457850799998</v>
+      </c>
+      <c r="F21" s="44"/>
+      <c r="H21" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="6">
+        <v>11756.38396171659</v>
+      </c>
+      <c r="J21" s="42">
+        <v>2.5787396836160377</v>
+      </c>
+      <c r="K21" s="6">
+        <v>221475.25113283962</v>
+      </c>
+      <c r="L21" s="42">
+        <v>1304.8422799097152</v>
+      </c>
+      <c r="M21" s="6">
+        <v>242415.36519831017</v>
+      </c>
+      <c r="N21" s="42">
+        <v>1402.8343878871244</v>
+      </c>
+      <c r="O21" s="6">
+        <v>13266.326302362706</v>
+      </c>
+      <c r="P21" s="42">
+        <v>5540.4222102490567</v>
+      </c>
+      <c r="Q21" s="6">
+        <v>187474.37499888588</v>
+      </c>
+      <c r="R21" s="42">
+        <v>86426.46049639149</v>
+      </c>
+      <c r="S21" s="6">
+        <v>1347.3914846893797</v>
+      </c>
+      <c r="T21" s="42">
+        <v>954.13368293793394</v>
+      </c>
+      <c r="U21" s="6">
+        <v>0</v>
+      </c>
+      <c r="V21" s="42">
+        <v>0</v>
+      </c>
+      <c r="W21" s="6">
+        <v>0</v>
+      </c>
+      <c r="X21" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="44">
+        <f>(11800*B17+44400*1702+96000*2858281)/(B17+1702+2858281)</f>
+        <v>53897.172393579589</v>
+      </c>
+      <c r="C22" s="44"/>
+      <c r="D22">
+        <v>50000</v>
+      </c>
+      <c r="E22">
+        <f>E20</f>
+        <v>25000</v>
+      </c>
+      <c r="F22">
+        <f>F20</f>
+        <v>58428.749587197526</v>
+      </c>
+      <c r="H22" t="s">
+        <v>155</v>
+      </c>
+      <c r="I22" s="6">
+        <v>262101.48871328257</v>
+      </c>
+      <c r="J22" s="42">
+        <v>11798.526229932957</v>
+      </c>
+      <c r="K22" s="6">
+        <v>407170.21610996046</v>
+      </c>
+      <c r="L22" s="42">
+        <v>28998.536093459767</v>
+      </c>
+      <c r="M22" s="6">
+        <v>6223.9972815333149</v>
+      </c>
+      <c r="N22" s="42">
+        <v>93.299351525193202</v>
+      </c>
+      <c r="O22" s="6">
+        <v>0</v>
+      </c>
+      <c r="P22" s="42">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>246.67250903831379</v>
+      </c>
+      <c r="R22" s="42">
+        <v>248.06651111404307</v>
+      </c>
+      <c r="S22" s="6">
+        <v>0</v>
+      </c>
+      <c r="T22" s="42">
+        <v>0</v>
+      </c>
+      <c r="U22" s="6">
+        <v>0</v>
+      </c>
+      <c r="V22" s="42">
+        <v>0</v>
+      </c>
+      <c r="W22" s="6">
+        <v>0</v>
+      </c>
+      <c r="X22" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="A23" t="s">
+        <v>42</v>
+      </c>
+      <c r="B23" s="44">
+        <f>B22/converter!$D$2/2.95</f>
+        <v>11352.903703490325</v>
+      </c>
+      <c r="C23" s="44"/>
+      <c r="D23">
+        <f>D22/converter!$D$2</f>
+        <v>31069.409059839683</v>
+      </c>
+      <c r="E23">
+        <f>E22/converter!$D$2</f>
+        <v>15534.704529919842</v>
+      </c>
+      <c r="F23">
+        <f>F22/converter!$D$2</f>
+        <v>36306.934435591582</v>
+      </c>
+      <c r="H23" t="s">
+        <v>156</v>
+      </c>
+      <c r="I23" s="6">
+        <v>75554.380396783235</v>
+      </c>
+      <c r="J23" s="42">
+        <v>5684.8316325315554</v>
+      </c>
+      <c r="K23" s="6">
+        <v>758715.48977083596</v>
+      </c>
+      <c r="L23" s="42">
+        <v>53795.088539914148</v>
+      </c>
+      <c r="M23" s="6">
+        <v>70979.911136000985</v>
+      </c>
+      <c r="N23" s="42">
+        <v>1101.1218449040482</v>
+      </c>
+      <c r="O23" s="6">
+        <v>114.8828529050945</v>
+      </c>
+      <c r="P23" s="42">
+        <v>5.1574793672320753</v>
+      </c>
+      <c r="Q23" s="6">
+        <v>12688.172865295992</v>
+      </c>
+      <c r="R23" s="42">
+        <v>5005.3337258987294</v>
+      </c>
+      <c r="S23" s="6">
+        <v>725.03844944548507</v>
+      </c>
+      <c r="T23" s="42">
+        <v>562.16525102829621</v>
+      </c>
+      <c r="U23" s="6">
+        <v>6.3823807169496929</v>
+      </c>
+      <c r="V23" s="42">
+        <v>0</v>
+      </c>
+      <c r="W23" s="6">
+        <v>0</v>
+      </c>
+      <c r="X23" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="H24" t="s">
+        <v>157</v>
+      </c>
+      <c r="I24" s="6">
+        <v>7715647.1048477273</v>
+      </c>
+      <c r="J24" s="42">
+        <v>1163639.2761537712</v>
+      </c>
+      <c r="K24" s="6">
+        <v>11001245.171946557</v>
+      </c>
+      <c r="L24" s="42">
+        <v>1127332.5174063188</v>
+      </c>
+      <c r="M24" s="6">
+        <v>146358.69042895696</v>
+      </c>
+      <c r="N24" s="42">
+        <v>35151.051968430264</v>
+      </c>
+      <c r="O24" s="6">
+        <v>106.03797138383194</v>
+      </c>
+      <c r="P24" s="42">
+        <v>104.96688076379323</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>62983.341730136061</v>
+      </c>
+      <c r="R24" s="42">
+        <v>19423.157303781903</v>
+      </c>
+      <c r="S24" s="6">
+        <v>0</v>
+      </c>
+      <c r="T24" s="42">
+        <v>0</v>
+      </c>
+      <c r="U24" s="6">
+        <v>0</v>
+      </c>
+      <c r="V24" s="42">
+        <v>0</v>
+      </c>
+      <c r="W24" s="6">
+        <v>0</v>
+      </c>
+      <c r="X24" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="H25" t="s">
+        <v>158</v>
+      </c>
+      <c r="I25" s="6">
+        <v>9030.7627098073899</v>
+      </c>
+      <c r="J25" s="42">
+        <v>29.654263802499546</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1098475.4350233979</v>
+      </c>
+      <c r="L25" s="42">
+        <v>83252.36867459731</v>
+      </c>
+      <c r="M25" s="6">
+        <v>1575.6990766550152</v>
+      </c>
+      <c r="N25" s="42">
+        <v>215.48765029816337</v>
+      </c>
+      <c r="O25" s="6">
+        <v>0</v>
+      </c>
+      <c r="P25" s="42">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>1871.1840459377215</v>
+      </c>
+      <c r="R25" s="42">
+        <v>887.65096315481969</v>
+      </c>
+      <c r="S25" s="6">
+        <v>2390.1336624814635</v>
+      </c>
+      <c r="T25" s="42">
+        <v>1990.7895766078029</v>
+      </c>
+      <c r="U25" s="6">
+        <v>0</v>
+      </c>
+      <c r="V25" s="42">
+        <v>0</v>
+      </c>
+      <c r="W25" s="6">
+        <v>0</v>
+      </c>
+      <c r="X25" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="H26" t="s">
+        <v>159</v>
+      </c>
+      <c r="I26" s="6">
+        <v>34095.052238180331</v>
+      </c>
+      <c r="J26" s="42">
+        <v>0</v>
+      </c>
+      <c r="K26" s="6">
+        <v>7037095.2327644899</v>
+      </c>
+      <c r="L26" s="42">
+        <v>1211734.8571893964</v>
+      </c>
+      <c r="M26" s="6">
+        <v>311949.39093249157</v>
+      </c>
+      <c r="N26" s="42">
+        <v>132946.23824651662</v>
+      </c>
+      <c r="O26" s="6">
+        <v>2.2237179455635459</v>
+      </c>
+      <c r="P26" s="42">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>6356.4977473933941</v>
+      </c>
+      <c r="R26" s="42">
+        <v>5804.5915857390719</v>
+      </c>
+      <c r="S26" s="6">
+        <v>0</v>
+      </c>
+      <c r="T26" s="42">
+        <v>0</v>
+      </c>
+      <c r="U26" s="6">
+        <v>14.454166646163049</v>
+      </c>
+      <c r="V26" s="42">
+        <v>0</v>
+      </c>
+      <c r="W26" s="6">
+        <v>0</v>
+      </c>
+      <c r="X26" s="42">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+  </mergeCells>
   <phoneticPr fontId="42" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{B5F31804-759C-4FF2-ABBA-8D0A267F9D99}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{B5F31804-759C-4FF2-ABBA-8D0A267F9D99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
@@ -5356,8 +6977,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
@@ -5409,10 +7030,10 @@
         <v>47</v>
       </c>
       <c r="E5">
-        <v>13641.806552303125</v>
+        <v>76754</v>
       </c>
       <c r="F5">
-        <v>7358.1934476968736</v>
+        <v>877046</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -5420,10 +7041,10 @@
         <v>48</v>
       </c>
       <c r="E6" s="8">
-        <v>13456.92</v>
+        <v>14706.6</v>
       </c>
       <c r="F6" s="8">
-        <v>26962.2</v>
+        <v>30182</v>
       </c>
       <c r="I6" t="s">
         <v>74</v>
@@ -5435,25 +7056,433 @@
       </c>
       <c r="E8">
         <f>E6/E5/E4*10^8</f>
-        <v>137860.50569468629</v>
+        <v>26777.951208971313</v>
       </c>
       <c r="F8">
         <f>F6/F5/F4*10^8</f>
-        <v>91606.044987982794</v>
+        <v>860.33115708868172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="D9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9">
+        <f>E8/converter!$D$2</f>
+        <v>16639.502397919165</v>
+      </c>
+      <c r="F9">
+        <f>F8/converter!$D$2</f>
+        <v>534.5996129302689</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11">
+      <c r="C18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D18">
+        <v>21700</v>
+      </c>
+      <c r="E18">
+        <v>21800</v>
+      </c>
+      <c r="F18">
+        <v>22000</v>
+      </c>
+      <c r="G18">
+        <v>22100</v>
+      </c>
+      <c r="H18">
+        <v>22400</v>
+      </c>
+      <c r="I18">
+        <f>7800+14700</f>
+        <v>22500</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19">
+        <v>76000</v>
+      </c>
+      <c r="E19">
+        <v>76000</v>
+      </c>
+      <c r="F19">
+        <v>78000</v>
+      </c>
+      <c r="G19">
+        <v>77000</v>
+      </c>
+      <c r="H19">
+        <v>78000</v>
+      </c>
+      <c r="I19">
+        <v>81000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="C20" t="s">
+        <v>171</v>
+      </c>
+      <c r="D20">
+        <v>878000</v>
+      </c>
+      <c r="E20">
+        <v>912000</v>
+      </c>
+      <c r="F20">
+        <v>966000</v>
+      </c>
+      <c r="G20">
+        <v>997000</v>
+      </c>
+      <c r="H20">
+        <v>1007000</v>
+      </c>
+      <c r="I20">
+        <v>1019000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="D21">
+        <v>2019</v>
+      </c>
+      <c r="E21">
+        <v>2020</v>
+      </c>
+      <c r="F21">
+        <v>2021</v>
+      </c>
+      <c r="G21">
+        <v>2022</v>
+      </c>
+      <c r="H21">
+        <v>2023</v>
+      </c>
+      <c r="I21">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="B22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22">
+        <f>D19+D18*D19/(D19+D20)</f>
+        <v>77728.721174004197</v>
+      </c>
+      <c r="E22">
+        <f>E19+E18*E19/(E19+E20)</f>
+        <v>77676.923076923078</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:I22" si="0">F19+F18*F19/(F19+F20)</f>
+        <v>79643.678160919546</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>78584.45065176909</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>79610.322580645166</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>82656.818181818177</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="C23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23">
+        <v>14706.6</v>
+      </c>
+      <c r="E23">
+        <v>8266.2000000000007</v>
+      </c>
+      <c r="F23">
+        <v>9567.7999999999993</v>
+      </c>
+      <c r="G23">
+        <v>6577.5</v>
+      </c>
+      <c r="H23">
+        <v>14729.4</v>
+      </c>
+      <c r="I23">
+        <v>15799.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="C24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24">
+        <f>D23*10^8/D22/$E$4</f>
+        <v>26442.154663683945</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ref="E24:I24" si="1">E23*10^8/E22/$E$4</f>
+        <v>14872.363037220844</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>16789.078631927241</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>11697.426326362638</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>25857.215559973622</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>26712.820627048746</v>
+      </c>
+      <c r="J24">
+        <f>J25*K25</f>
+        <v>1.6714855159715003</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="C25" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="52">
+        <f>D24/converter!$D$2</f>
+        <v>16430.842393390882</v>
+      </c>
+      <c r="E25" s="52">
+        <f>E24/converter!$D$2*$J$25</f>
+        <v>16430.860300226996</v>
+      </c>
+      <c r="F25" s="52">
+        <f>F24/converter!$D$2*$J$25</f>
+        <v>18548.431401273247</v>
+      </c>
+      <c r="G25" s="52">
+        <f>G24/converter!$D$2*$J$25</f>
+        <v>12923.217202246135</v>
+      </c>
+      <c r="H25" s="52">
+        <f>H24/converter!$D$2*$J$25</f>
+        <v>28566.832019599085</v>
+      </c>
+      <c r="I25" s="52">
+        <f>I24/converter!$D$2*$J$25</f>
+        <v>29512.097226889557</v>
+      </c>
+      <c r="J25">
+        <v>1.7779409643900461</v>
+      </c>
+      <c r="K25">
+        <v>0.94012430640234035</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="C26" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="52">
+        <f>D23/$D$23</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="52">
+        <f>E23/$D$23</f>
+        <v>0.56207417078046595</v>
+      </c>
+      <c r="F26" s="52">
+        <f t="shared" ref="F26:I26" si="2">F23/$D$23</f>
+        <v>0.65057865176179397</v>
+      </c>
+      <c r="G26" s="52">
+        <f t="shared" si="2"/>
+        <v>0.44724817428909469</v>
+      </c>
+      <c r="H26" s="52">
+        <f t="shared" si="2"/>
+        <v>1.0015503243441719</v>
+      </c>
+      <c r="I26" s="52">
+        <f t="shared" si="2"/>
+        <v>1.0742863748249085</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27">
+        <f>D20+D18*D20/(D19+D20)</f>
+        <v>897971.27882599586</v>
+      </c>
+      <c r="E27">
+        <f>E20+E18*E20/(E19+E20)</f>
+        <v>932123.07692307688</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ref="F27:I27" si="3">F20+F18*F20/(F19+F20)</f>
+        <v>986356.32183908042</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>1017515.5493482309</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="3"/>
+        <v>1027789.6774193548</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>1039843.1818181818</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="C28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28">
+        <v>30182</v>
+      </c>
+      <c r="E28">
+        <v>30514.5</v>
+      </c>
+      <c r="F28">
+        <v>33238</v>
+      </c>
+      <c r="G28">
+        <v>35945.699999999997</v>
+      </c>
+      <c r="H28">
+        <v>36460.400000000001</v>
+      </c>
+      <c r="I28">
+        <v>35861.9</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="C29" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29">
+        <f>D28*10^8/D27/$F$4</f>
+        <v>840.2829999045133</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29:I29" si="4">E28*10^8/E27/$F$4</f>
+        <v>818.41391859774217</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="4"/>
+        <v>842.44403528602902</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="4"/>
+        <v>883.17323560865952</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="4"/>
+        <v>886.86432645313403</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="4"/>
+        <v>862.19491138305386</v>
+      </c>
+      <c r="J29">
+        <v>0.87166617226265275</v>
+      </c>
+      <c r="K29">
+        <f>J29*J30</f>
+        <v>0.89551300438741477</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="C30" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="52">
+        <f>D29/converter!$D$2</f>
+        <v>522.14192500125102</v>
+      </c>
+      <c r="E30" s="52">
+        <f>E29/converter!$D$2*$J$30</f>
+        <v>522.46559899225224</v>
+      </c>
+      <c r="F30" s="52">
+        <f>F29/converter!$D$2*$J$30</f>
+        <v>537.80613637083309</v>
+      </c>
+      <c r="G30" s="52">
+        <f>G29/converter!$D$2*$J$30</f>
+        <v>563.80716782872753</v>
+      </c>
+      <c r="H30" s="52">
+        <f>H29/converter!$D$2*$J$30</f>
+        <v>566.16351581496099</v>
+      </c>
+      <c r="I30" s="52">
+        <f>I29/converter!$D$2*$J$30</f>
+        <v>550.41485804107867</v>
+      </c>
+      <c r="J30">
+        <v>1.0273577579164979</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="C31" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="52">
+        <f>D28/$D$28</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="52">
+        <f t="shared" ref="E31:I31" si="5">E28/$D$28</f>
+        <v>1.011016499900603</v>
+      </c>
+      <c r="F31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.1012524020939634</v>
+      </c>
+      <c r="G31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.1909648134649791</v>
+      </c>
+      <c r="H31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.2080180239878073</v>
+      </c>
+      <c r="I31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.1881883241667219</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="42" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="F2:M12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="C2:M33"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="6" max="6" width="19.5" customWidth="1"/>
     <col min="7" max="7" width="15.5" customWidth="1"/>
@@ -5484,11 +7513,11 @@
       <c r="F8" t="s">
         <v>46</v>
       </c>
-      <c r="G8">
-        <v>239.7</v>
+      <c r="G8" s="53">
+        <v>239.70073166222036</v>
       </c>
       <c r="H8">
-        <v>29.5</v>
+        <v>29.511670253269312</v>
       </c>
     </row>
     <row r="9" spans="6:13">
@@ -5496,7 +7525,7 @@
         <v>47</v>
       </c>
       <c r="G9">
-        <v>3479</v>
+        <v>3645</v>
       </c>
       <c r="H9">
         <v>173</v>
@@ -5507,10 +7536,10 @@
         <v>48</v>
       </c>
       <c r="G10" s="8">
-        <v>9512.7999999999993</v>
+        <v>11705.3</v>
       </c>
       <c r="H10" s="8">
-        <v>243.5</v>
+        <v>263.2</v>
       </c>
       <c r="I10" t="s">
         <v>50</v>
@@ -5525,11 +7554,327 @@
       </c>
       <c r="G12">
         <f>G10/G9/G8*10^8</f>
-        <v>1140737.9853349791</v>
+        <v>1339724.9843919652</v>
       </c>
       <c r="H12">
         <f>H10/H9/H8*10^8</f>
-        <v>4771235.4266679734</v>
+        <v>5155205.6192700732</v>
+      </c>
+    </row>
+    <row r="13" spans="6:13">
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13">
+        <f>G12/converter!$D$2</f>
+        <v>832489.27135522605</v>
+      </c>
+      <c r="H13">
+        <f>H12/converter!$D$2</f>
+        <v>3203383.8434537211</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11">
+      <c r="F22">
+        <v>1.8912417621455959</v>
+      </c>
+      <c r="G22">
+        <v>1.1780617896301924</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11">
+      <c r="E23">
+        <v>2019</v>
+      </c>
+      <c r="F23">
+        <v>2020</v>
+      </c>
+      <c r="G23">
+        <v>2021</v>
+      </c>
+      <c r="H23">
+        <v>2022</v>
+      </c>
+      <c r="I23">
+        <v>2023</v>
+      </c>
+      <c r="J23">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11">
+      <c r="C24" t="s">
+        <v>163</v>
+      </c>
+      <c r="D24" t="s">
+        <v>161</v>
+      </c>
+      <c r="E24">
+        <v>3645</v>
+      </c>
+      <c r="F24">
+        <v>3717</v>
+      </c>
+      <c r="G24">
+        <v>3856</v>
+      </c>
+      <c r="H24">
+        <v>3942</v>
+      </c>
+      <c r="I24">
+        <v>4013</v>
+      </c>
+      <c r="J24">
+        <v>4126</v>
+      </c>
+      <c r="K24" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11">
+      <c r="D25" t="s">
+        <v>162</v>
+      </c>
+      <c r="E25">
+        <v>11705.3</v>
+      </c>
+      <c r="F25">
+        <v>6311.3</v>
+      </c>
+      <c r="G25">
+        <v>6529.7</v>
+      </c>
+      <c r="H25">
+        <v>3913.9</v>
+      </c>
+      <c r="I25">
+        <v>10309</v>
+      </c>
+      <c r="J25">
+        <v>12914.7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11">
+      <c r="D26" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26">
+        <f>E25*10^8/E24/$G$8</f>
+        <v>1339724.9843919654</v>
+      </c>
+      <c r="F26">
+        <f>F25*10^8/F24/$G$8</f>
+        <v>708364.68814827537</v>
+      </c>
+      <c r="G26">
+        <f t="shared" ref="G26:J26" si="0">G25*10^8/G24/$G$8</f>
+        <v>706458.80707901006</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>414213.01965868712</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>1071711.8190267321</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="0"/>
+        <v>1305827.2852361202</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11">
+      <c r="D27" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="52">
+        <f>E26/converter!$D$2</f>
+        <v>832489.27135522617</v>
+      </c>
+      <c r="F27" s="52">
+        <f>(F26/converter!$D$2)*1.8912417621456</f>
+        <v>832466.83716849552</v>
+      </c>
+      <c r="G27" s="52">
+        <f>(G26/converter!$D$2)*1.8912417621456</f>
+        <v>830227.05473397288</v>
+      </c>
+      <c r="H27" s="52">
+        <f>(H26/converter!$D$2)*1.8912417621456</f>
+        <v>486781.18511336844</v>
+      </c>
+      <c r="I27" s="52">
+        <f>(I26/converter!$D$2)*1.8912417621456</f>
+        <v>1259470.6699362323</v>
+      </c>
+      <c r="J27" s="52">
+        <f>J26/converter!$D$2</f>
+        <v>811425.64173001947</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11">
+      <c r="D28" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="E28" s="52">
+        <f>E26/$E$26</f>
+        <v>1</v>
+      </c>
+      <c r="F28" s="52">
+        <f t="shared" ref="F28:J28" si="1">F26/$E$26</f>
+        <v>0.52873888029323191</v>
+      </c>
+      <c r="G28" s="52">
+        <f t="shared" si="1"/>
+        <v>0.52731628902153871</v>
+      </c>
+      <c r="H28" s="52">
+        <f t="shared" si="1"/>
+        <v>0.30917764801309411</v>
+      </c>
+      <c r="I28" s="52">
+        <f t="shared" si="1"/>
+        <v>0.79994911755200926</v>
+      </c>
+      <c r="J28" s="52">
+        <f t="shared" si="1"/>
+        <v>0.97469801671928236</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11">
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" t="s">
+        <v>161</v>
+      </c>
+      <c r="E29">
+        <v>173</v>
+      </c>
+      <c r="F29">
+        <v>186</v>
+      </c>
+      <c r="G29">
+        <v>198</v>
+      </c>
+      <c r="H29">
+        <v>223</v>
+      </c>
+      <c r="I29">
+        <v>257</v>
+      </c>
+      <c r="J29">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11">
+      <c r="D30" t="s">
+        <v>162</v>
+      </c>
+      <c r="E30">
+        <v>263.2</v>
+      </c>
+      <c r="F30">
+        <v>240.2</v>
+      </c>
+      <c r="G30">
+        <v>278.16000000000003</v>
+      </c>
+      <c r="H30">
+        <v>254.1</v>
+      </c>
+      <c r="I30">
+        <v>283.62</v>
+      </c>
+      <c r="J30">
+        <v>353.89</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11">
+      <c r="D31" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31">
+        <f>E30*10^8/E29/$H$8</f>
+        <v>5155205.6192700732</v>
+      </c>
+      <c r="F31">
+        <f>F30*10^8/F29/$H$8</f>
+        <v>4375888.7192069525</v>
+      </c>
+      <c r="G31">
+        <f t="shared" ref="G31:J31" si="2">G30*10^8/G29/$H$8</f>
+        <v>4760315.0644882778</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="2"/>
+        <v>3861055.2152053872</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>3739469.0204452593</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="2"/>
+        <v>4474450.4912614422</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11">
+      <c r="D32" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="52">
+        <f>E31/converter!$D$2</f>
+        <v>3203383.8434537211</v>
+      </c>
+      <c r="F32" s="52">
+        <f>(F31/converter!$D$2)*1.17806178963019</f>
+        <v>3203297.8908665339</v>
+      </c>
+      <c r="G32" s="52">
+        <f>(G31/converter!$D$2)*1.17806178963019</f>
+        <v>3484710.9203222673</v>
+      </c>
+      <c r="H32" s="52">
+        <f>(H31/converter!$D$2)*1.17806178963019</f>
+        <v>2826422.4300539652</v>
+      </c>
+      <c r="I32" s="52">
+        <f>(I31/converter!$D$2)*1.17806178963019</f>
+        <v>2737417.24134245</v>
+      </c>
+      <c r="J32" s="52">
+        <f>(J31/converter!$D$2)*1.17806178963019</f>
+        <v>3275448.4268608387</v>
+      </c>
+    </row>
+    <row r="33" spans="4:10">
+      <c r="D33" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="E33" s="52">
+        <f>E30/$E$30</f>
+        <v>1</v>
+      </c>
+      <c r="F33" s="52">
+        <f t="shared" ref="F33:J33" si="3">F30/$E$30</f>
+        <v>0.91261398176291797</v>
+      </c>
+      <c r="G33" s="52">
+        <f t="shared" si="3"/>
+        <v>1.0568389057750762</v>
+      </c>
+      <c r="H33" s="52">
+        <f t="shared" si="3"/>
+        <v>0.96542553191489366</v>
+      </c>
+      <c r="I33" s="52">
+        <f t="shared" si="3"/>
+        <v>1.0775835866261398</v>
+      </c>
+      <c r="J33" s="52">
+        <f t="shared" si="3"/>
+        <v>1.3445668693009118</v>
       </c>
     </row>
   </sheetData>
@@ -5543,41 +7888,10 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <sheetPr codeName="Sheet5"/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="B1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="B3">
-        <f>B2/converter!D2</f>
-        <v>3728.3290871807621</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="42" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A2:L15"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <dimension ref="A2:L31"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="2" width="10.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.625" bestFit="1" customWidth="1"/>
@@ -5623,25 +7937,25 @@
         <v>9</v>
       </c>
       <c r="B14" s="8">
-        <v>77.66</v>
+        <v>80.2</v>
       </c>
       <c r="D14">
-        <v>5753</v>
+        <v>5853</v>
       </c>
       <c r="F14">
         <v>17.53</v>
       </c>
       <c r="H14">
         <f>B14/D14/F14</f>
-        <v>7.7005384923305468E-4</v>
+        <v>7.8165287224780467E-4</v>
       </c>
       <c r="I14">
         <f>H14*10^8</f>
-        <v>77005.384923305464</v>
+        <v>78165.287224780463</v>
       </c>
       <c r="J14">
         <f>I14/converter!D2</f>
-        <v>47850.236079851777</v>
+        <v>48570.985661331302</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5649,39 +7963,416 @@
         <v>10</v>
       </c>
       <c r="B15" s="8">
-        <v>98611.25</v>
+        <v>103963</v>
       </c>
       <c r="D15">
-        <f>119721+279</f>
-        <v>120000</v>
+        <v>120998</v>
       </c>
       <c r="F15">
         <v>2258</v>
       </c>
       <c r="H15">
         <f>B15/D15/F15</f>
-        <v>3.6393286832004724E-4</v>
+        <v>3.8051928652247632E-4</v>
       </c>
       <c r="I15">
         <f>H15*10^8</f>
-        <v>36393.286832004727</v>
+        <v>38051.928652247632</v>
       </c>
       <c r="J15">
         <f>I15/converter!D2</f>
-        <v>22614.358312312637</v>
+        <v>23645.018736250317</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="C20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20">
+        <f>D22+D27</f>
+        <v>131528</v>
+      </c>
+      <c r="E20">
+        <f>11.5*10^4+10352+1499</f>
+        <v>126851</v>
+      </c>
+      <c r="F20">
+        <f>11.36*10^4+10891+1402</f>
+        <v>125893</v>
+      </c>
+      <c r="G20">
+        <f>10.95*10^4+10997+1387</f>
+        <v>121884</v>
+      </c>
+      <c r="H20">
+        <f>10.66*10^4+10672+972</f>
+        <v>118244</v>
+      </c>
+      <c r="I20">
+        <f>9.87*10^4+10245+1217</f>
+        <v>110161.99999999999</v>
+      </c>
+      <c r="J20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="D21">
+        <v>2019</v>
+      </c>
+      <c r="E21">
+        <v>2020</v>
+      </c>
+      <c r="F21">
+        <v>2021</v>
+      </c>
+      <c r="G21">
+        <v>2022</v>
+      </c>
+      <c r="H21">
+        <v>2023</v>
+      </c>
+      <c r="I21">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="54">
+        <v>17.533087393027898</v>
+      </c>
+      <c r="B22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C22" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22">
+        <v>5853</v>
+      </c>
+      <c r="E22">
+        <f>E20*$D22/$D$20</f>
+        <v>5644.873357764126</v>
+      </c>
+      <c r="F22">
+        <f t="shared" ref="F22:I22" si="0">F20*$D22/$D$20</f>
+        <v>5602.2423286296453</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>5423.8417067088376</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>5261.8615960099751</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>4902.2123502220047</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="C23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23">
+        <v>80.2</v>
+      </c>
+      <c r="E23">
+        <v>33</v>
+      </c>
+      <c r="F23">
+        <v>33.1</v>
+      </c>
+      <c r="G23">
+        <v>22.6</v>
+      </c>
+      <c r="H23">
+        <v>53.8</v>
+      </c>
+      <c r="I23">
+        <v>54.7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="C24" t="s">
+        <v>164</v>
+      </c>
+      <c r="D24">
+        <f>D23*10^8/D22/$A$22</f>
+        <v>78151.523136494594</v>
+      </c>
+      <c r="E24">
+        <f t="shared" ref="E24:I24" si="1">E23*10^8/E22/$A$22</f>
+        <v>33342.744102506782</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>33698.277759219913</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="1"/>
+        <v>23765.285464302418</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>58315.56095344534</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="1"/>
+        <v>63640.972726790169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="C25" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="52">
+        <f>D24/converter!$D$2</f>
+        <v>48562.432819545516</v>
+      </c>
+      <c r="E25" s="52">
+        <f>E24/converter!$D$2*$J$25</f>
+        <v>20718.787113966806</v>
+      </c>
+      <c r="F25" s="52">
+        <f>F24/converter!$D$2*$J$25</f>
+        <v>20939.711526266026</v>
+      </c>
+      <c r="G25" s="52">
+        <f>G24/converter!$D$2*$J$25</f>
+        <v>14767.467510285478</v>
+      </c>
+      <c r="H25" s="52">
+        <f>H24/converter!$D$2*$J$25</f>
+        <v>36236.600356332157</v>
+      </c>
+      <c r="I25" s="52">
+        <f>I24/converter!$D$2*$J$25</f>
+        <v>39545.748292294891</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="C26" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D26" s="52">
+        <f>D24/$D$24</f>
+        <v>1</v>
+      </c>
+      <c r="E26" s="52">
+        <f>E23/$D$23</f>
+        <v>0.41147132169576056</v>
+      </c>
+      <c r="F26" s="52">
+        <f t="shared" ref="F26:I26" si="2">F23/$D$23</f>
+        <v>0.41271820448877805</v>
+      </c>
+      <c r="G26" s="52">
+        <f t="shared" si="2"/>
+        <v>0.28179551122194513</v>
+      </c>
+      <c r="H26" s="52">
+        <f t="shared" si="2"/>
+        <v>0.67082294264339148</v>
+      </c>
+      <c r="I26" s="52">
+        <f t="shared" si="2"/>
+        <v>0.68204488778054861</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27">
+        <v>2257.5222609676471</v>
+      </c>
+      <c r="B27" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27">
+        <v>125675</v>
+      </c>
+      <c r="E27">
+        <f>E20*$D27/$D$20</f>
+        <v>121206.12664223587</v>
+      </c>
+      <c r="F27">
+        <f t="shared" ref="F27:I27" si="3">F20*$D27/$D$20</f>
+        <v>120290.75767137036</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="3"/>
+        <v>116460.15829329116</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="3"/>
+        <v>112982.13840399003</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="3"/>
+        <v>105259.78764977798</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="C28" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28">
+        <v>103963</v>
+      </c>
+      <c r="E28">
+        <v>105834.4</v>
+      </c>
+      <c r="F28">
+        <v>115577.5</v>
+      </c>
+      <c r="G28">
+        <v>121003.1</v>
+      </c>
+      <c r="H28">
+        <v>129951.5</v>
+      </c>
+      <c r="I28">
+        <v>141422.9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="C29" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29">
+        <f>D28*10^8/D27/$A$27</f>
+        <v>36643.577559852056</v>
+      </c>
+      <c r="E29">
+        <f t="shared" ref="E29:I29" si="4">E28*10^8/E27/$A$27</f>
+        <v>38678.554725277514</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="4"/>
+        <v>42560.722748314729</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="4"/>
+        <v>46024.288054108634</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="4"/>
+        <v>50949.445875406062</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="4"/>
+        <v>59514.831390512096</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="C30" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="52">
+        <f>D29/converter!$D$2</f>
+        <v>22769.886012460112</v>
+      </c>
+      <c r="E30" s="52">
+        <f>E29/converter!$D$2*$J$30</f>
+        <v>22769.630777300627</v>
+      </c>
+      <c r="F30" s="52">
+        <f>F29/converter!$D$2*$J$30</f>
+        <v>25055.019492774827</v>
+      </c>
+      <c r="G30" s="52">
+        <f>G29/converter!$D$2*$J$30</f>
+        <v>27093.981489833517</v>
+      </c>
+      <c r="H30" s="52">
+        <f>H29/converter!$D$2*$J$30</f>
+        <v>29993.366585977961</v>
+      </c>
+      <c r="I30" s="52">
+        <f>I29/converter!$D$2*$J$30</f>
+        <v>35035.712842952897</v>
+      </c>
+      <c r="J30">
+        <v>0.94737683634188563</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="C31" s="52" t="s">
+        <v>167</v>
+      </c>
+      <c r="D31" s="52">
+        <f>D28/$D$28</f>
+        <v>1</v>
+      </c>
+      <c r="E31" s="52">
+        <f t="shared" ref="E31:I31" si="5">E28/$D$28</f>
+        <v>1.0180006348412416</v>
+      </c>
+      <c r="F31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.1117176303107836</v>
+      </c>
+      <c r="G31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.1639054278926158</v>
+      </c>
+      <c r="H31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.2499783576849457</v>
+      </c>
+      <c r="I31" s="52">
+        <f t="shared" si="5"/>
+        <v>1.3603195367582697</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="42" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="B3">
+        <f>B2/converter!D2</f>
+        <v>3728.3290871807621</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="42" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:O53"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
@@ -7787,7 +10478,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A2:E2"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <sheetData>
     <row r="2" spans="1:5">
       <c r="A2">
@@ -7815,7 +10506,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4415DE-EDB6-47B2-AFE3-CE3361DF00AD}">
   <dimension ref="A1:W53"/>
-  <sheetFormatPr defaultRowHeight="13.5" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="13.6" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -7833,86 +10524,89 @@
     <col min="16" max="21" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="13.5" customHeight="1">
-      <c r="A1" s="41" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="H1" s="42" t="s">
+    <row r="1" spans="1:21" ht="13.6" customHeight="1">
+      <c r="A1" s="49" t="s">
         <v>125</v>
       </c>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="40"/>
-    </row>
-    <row r="2" spans="1:21" s="37" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="H1" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
+      <c r="N1" s="36"/>
+    </row>
+    <row r="2" spans="1:21" s="34" customFormat="1" ht="13.6" customHeight="1">
+      <c r="A2" s="48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="48" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="I2" s="48" t="s">
+        <v>121</v>
+      </c>
+      <c r="J2" s="48" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="K2" s="48" t="s">
         <v>114</v>
       </c>
-      <c r="E2" s="38" t="s">
+      <c r="L2" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="38" t="s">
+      <c r="M2" s="35"/>
+      <c r="N2" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="38" t="s">
-        <v>123</v>
-      </c>
-      <c r="I2" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="38" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" s="38" t="s">
-        <v>113</v>
-      </c>
-      <c r="M2" s="39"/>
-      <c r="N2" s="38" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" s="37" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
+    </row>
+    <row r="3" spans="1:21" s="34" customFormat="1" ht="13.6" customHeight="1">
+      <c r="A3" s="48"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
       <c r="G3" s="11"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="N3" s="38"/>
-    </row>
-    <row r="4" spans="1:21" ht="13.5" customHeight="1">
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="48"/>
+      <c r="P3" s="34" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="13.6" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="30">
         <v>1743.1</v>
@@ -7930,7 +10624,7 @@
         <v>27.91</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I4" s="30">
         <v>9928</v>
@@ -7950,10 +10644,25 @@
       <c r="N4" s="29">
         <v>0.97</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="13.5" customHeight="1">
+      <c r="P4" s="43">
+        <v>2019</v>
+      </c>
+      <c r="Q4" s="43">
+        <v>2020</v>
+      </c>
+      <c r="R4" s="43">
+        <v>2021</v>
+      </c>
+      <c r="S4" s="43">
+        <v>2022</v>
+      </c>
+      <c r="T4" s="43">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="13.6" customHeight="1">
       <c r="A5" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B5" s="30">
         <v>2281.3000000000002</v>
@@ -7971,7 +10680,7 @@
         <v>39.56</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I5" s="30">
         <v>11629</v>
@@ -7991,10 +10700,25 @@
       <c r="N5" s="29">
         <v>1.41</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="13.5" customHeight="1">
+      <c r="P5">
+        <v>13100.62662088282</v>
+      </c>
+      <c r="Q5">
+        <v>11397.276942754101</v>
+      </c>
+      <c r="R5">
+        <v>11800</v>
+      </c>
+      <c r="S5">
+        <v>10327.241725629954</v>
+      </c>
+      <c r="T5">
+        <v>10503.774815011704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="13.6" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B6" s="30">
         <v>4435.3863000000001</v>
@@ -8012,7 +10736,7 @@
         <v>115.7163</v>
       </c>
       <c r="H6" s="23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I6" s="30">
         <v>18365</v>
@@ -8032,16 +10756,14 @@
       <c r="N6" s="29">
         <v>4.1500000000000004</v>
       </c>
-      <c r="P6" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="36"/>
-    </row>
-    <row r="7" spans="1:21" ht="13.5" customHeight="1">
+      <c r="P6" s="51"/>
+      <c r="Q6" s="51"/>
+      <c r="R6" s="51"/>
+      <c r="S6" s="51"/>
+      <c r="T6" s="51"/>
+      <c r="U6" s="51"/>
+    </row>
+    <row r="7" spans="1:21" ht="13.6" customHeight="1">
       <c r="A7" s="23" t="s">
         <v>116</v>
       </c>
@@ -8081,22 +10803,22 @@
       <c r="N7" s="29">
         <v>8.18</v>
       </c>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35" t="s">
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="S7" s="35" t="s">
+      <c r="S7" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="U7" s="35" t="s">
+      <c r="U7" s="46" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="13.5" customHeight="1">
+    <row r="8" spans="1:21" ht="13.6" customHeight="1">
       <c r="A8" s="23" t="s">
         <v>111</v>
       </c>
@@ -8136,14 +10858,14 @@
       <c r="N8" s="29">
         <v>10.1</v>
       </c>
-      <c r="P8" s="35"/>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="35"/>
-    </row>
-    <row r="9" spans="1:21" ht="13.5" customHeight="1">
+      <c r="P8" s="46"/>
+      <c r="Q8" s="46"/>
+      <c r="R8" s="46"/>
+      <c r="S8" s="46"/>
+      <c r="T8" s="46"/>
+      <c r="U8" s="46"/>
+    </row>
+    <row r="9" spans="1:21" ht="13.6" customHeight="1">
       <c r="A9" s="23" t="s">
         <v>110</v>
       </c>
@@ -8183,7 +10905,7 @@
       <c r="N9" s="29">
         <v>13.42</v>
       </c>
-      <c r="P9" s="34" t="s">
+      <c r="P9" s="47" t="s">
         <v>109</v>
       </c>
       <c r="Q9" s="33">
@@ -8202,7 +10924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="13.5" customHeight="1">
+    <row r="10" spans="1:21" ht="13.6" customHeight="1">
       <c r="A10" s="23" t="s">
         <v>108</v>
       </c>
@@ -8242,28 +10964,28 @@
       <c r="N10" s="29">
         <v>16.61</v>
       </c>
-      <c r="P10" s="34"/>
+      <c r="P10" s="47"/>
       <c r="Q10" s="33">
         <v>2020</v>
       </c>
       <c r="R10" s="32">
-        <f>C37/C$36</f>
+        <f t="shared" ref="R10:U12" si="0">C37/C$36</f>
         <v>0.56207349081364832</v>
       </c>
       <c r="S10" s="32">
-        <f>D37/D$36</f>
+        <f t="shared" si="0"/>
         <v>0.52398753542355847</v>
       </c>
       <c r="T10" s="32">
-        <f>E37/E$36</f>
+        <f t="shared" si="0"/>
         <v>0.41134663341645888</v>
       </c>
       <c r="U10" s="32">
-        <f>F37/F$36</f>
+        <f t="shared" si="0"/>
         <v>0.53919060922162132</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="13.5" customHeight="1">
+    <row r="11" spans="1:21" ht="13.6" customHeight="1">
       <c r="A11" s="23" t="s">
         <v>107</v>
       </c>
@@ -8303,28 +11025,28 @@
       <c r="N11" s="29">
         <v>18.579999999999998</v>
       </c>
-      <c r="P11" s="34"/>
+      <c r="P11" s="47"/>
       <c r="Q11" s="33">
         <v>2021</v>
       </c>
       <c r="R11" s="32">
-        <f>C38/C$36</f>
+        <f t="shared" si="0"/>
         <v>0.6505793317286116</v>
       </c>
       <c r="S11" s="32">
-        <f>D38/D$36</f>
+        <f t="shared" si="0"/>
         <v>0.4095629494981427</v>
       </c>
       <c r="T11" s="32">
-        <f>E38/E$36</f>
+        <f t="shared" si="0"/>
         <v>0.41284289276807978</v>
       </c>
       <c r="U11" s="32">
-        <f>F38/F$36</f>
+        <f t="shared" si="0"/>
         <v>0.55784914268139529</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="13.5" customHeight="1">
+    <row r="12" spans="1:21" ht="13.6" customHeight="1">
       <c r="A12" s="23" t="s">
         <v>106</v>
       </c>
@@ -8364,28 +11086,28 @@
       <c r="N12" s="29">
         <v>22.3</v>
       </c>
-      <c r="P12" s="34"/>
+      <c r="P12" s="47"/>
       <c r="Q12" s="33">
         <v>2022</v>
       </c>
       <c r="R12" s="32">
-        <f>C39/C$36</f>
+        <f t="shared" si="0"/>
         <v>0.44725021418954752</v>
       </c>
       <c r="S12" s="32">
-        <f>D39/D$36</f>
+        <f t="shared" si="0"/>
         <v>0.271820584615732</v>
       </c>
       <c r="T12" s="32">
-        <f>E39/E$36</f>
+        <f t="shared" si="0"/>
         <v>0.28182418952618454</v>
       </c>
       <c r="U12" s="32">
-        <f>F39/F$36</f>
+        <f t="shared" si="0"/>
         <v>0.33435852747947475</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="13.5" customHeight="1">
+    <row r="13" spans="1:21" ht="13.6" customHeight="1">
       <c r="A13" s="23" t="s">
         <v>105</v>
       </c>
@@ -8425,7 +11147,7 @@
       <c r="N13" s="29">
         <v>24.93</v>
       </c>
-      <c r="P13" s="34" t="s">
+      <c r="P13" s="47" t="s">
         <v>104</v>
       </c>
       <c r="Q13" s="33">
@@ -8444,7 +11166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="13.5" customHeight="1">
+    <row r="14" spans="1:21" ht="13.6" customHeight="1">
       <c r="A14" s="23" t="s">
         <v>103</v>
       </c>
@@ -8484,20 +11206,20 @@
       <c r="N14" s="29">
         <v>29.1</v>
       </c>
-      <c r="P14" s="34"/>
+      <c r="P14" s="47"/>
       <c r="Q14" s="33">
         <v>2020</v>
       </c>
       <c r="R14" s="32">
-        <f>J37/J$36</f>
+        <f t="shared" ref="R14:T16" si="1">J37/J$36</f>
         <v>1.0110168494746032</v>
       </c>
       <c r="S14" s="32">
-        <f>K37/K$36</f>
+        <f t="shared" si="1"/>
         <v>1.0089787460307373</v>
       </c>
       <c r="T14" s="32">
-        <f>L37/L$36</f>
+        <f t="shared" si="1"/>
         <v>1.0180006279154592</v>
       </c>
       <c r="U14" s="32">
@@ -8505,7 +11227,7 @@
         <v>0.91261398176291797</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="13.5" customHeight="1">
+    <row r="15" spans="1:21" ht="13.6" customHeight="1">
       <c r="A15" s="23" t="s">
         <v>102</v>
       </c>
@@ -8545,20 +11267,20 @@
       <c r="N15" s="29">
         <v>33.450000000000003</v>
       </c>
-      <c r="P15" s="34"/>
+      <c r="P15" s="47"/>
       <c r="Q15" s="33">
         <v>2021</v>
       </c>
       <c r="R15" s="32">
-        <f>J38/J$36</f>
+        <f t="shared" si="1"/>
         <v>1.1012542264499146</v>
       </c>
       <c r="S15" s="32">
-        <f>K38/K$36</f>
+        <f t="shared" si="1"/>
         <v>1.1584814238420533</v>
       </c>
       <c r="T15" s="32">
-        <f>L38/L$36</f>
+        <f t="shared" si="1"/>
         <v>1.111717298763099</v>
       </c>
       <c r="U15" s="32">
@@ -8566,7 +11288,7 @@
         <v>1.0568389057750762</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="13.5" customHeight="1">
+    <row r="16" spans="1:21" ht="13.6" customHeight="1">
       <c r="A16" s="23" t="s">
         <v>101</v>
       </c>
@@ -8606,20 +11328,20 @@
       <c r="N16" s="29">
         <v>42.34</v>
       </c>
-      <c r="P16" s="34"/>
+      <c r="P16" s="47"/>
       <c r="Q16" s="33">
         <v>2022</v>
       </c>
       <c r="R16" s="32">
-        <f>J39/J$36</f>
+        <f t="shared" si="1"/>
         <v>1.1909664551163859</v>
       </c>
       <c r="S16" s="32">
-        <f>K39/K$36</f>
+        <f t="shared" si="1"/>
         <v>1.1579848729944922</v>
       </c>
       <c r="T16" s="32">
-        <f>L39/L$36</f>
+        <f t="shared" si="1"/>
         <v>1.1639053398207673</v>
       </c>
       <c r="U16" s="32">
@@ -8627,7 +11349,7 @@
         <v>0.96542553191489366</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="13.5" customHeight="1">
+    <row r="17" spans="1:23" ht="13.6" customHeight="1">
       <c r="A17" s="23" t="s">
         <v>100</v>
       </c>
@@ -8668,7 +11390,7 @@
         <v>50.27</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="13.5" customHeight="1">
+    <row r="18" spans="1:23" ht="13.6" customHeight="1">
       <c r="A18" s="23" t="s">
         <v>99</v>
       </c>
@@ -8709,7 +11431,7 @@
         <v>43.72</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="13.5" customHeight="1">
+    <row r="19" spans="1:23" ht="13.6" customHeight="1">
       <c r="A19" s="23" t="s">
         <v>98</v>
       </c>
@@ -8749,17 +11471,17 @@
       <c r="N19" s="29">
         <v>51.55</v>
       </c>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="34" t="s">
+      <c r="P19" s="37"/>
+      <c r="Q19" s="47" t="s">
         <v>109</v>
       </c>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-    </row>
-    <row r="20" spans="1:23" ht="13.5" customHeight="1">
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+    </row>
+    <row r="20" spans="1:23" ht="13.6" customHeight="1">
       <c r="A20" s="23" t="s">
         <v>97</v>
       </c>
@@ -8799,9 +11521,9 @@
       <c r="N20" s="29">
         <v>57.9</v>
       </c>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
       <c r="S20" s="33">
         <v>2019</v>
       </c>
@@ -8818,7 +11540,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="13.5" customHeight="1">
+    <row r="21" spans="1:23" ht="13.6" customHeight="1">
       <c r="A21" s="23" t="s">
         <v>96</v>
       </c>
@@ -8858,13 +11580,13 @@
       <c r="N21" s="29">
         <v>71.8</v>
       </c>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="35" t="s">
+      <c r="P21" s="37"/>
+      <c r="Q21" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="R21" s="35"/>
+      <c r="R21" s="46"/>
       <c r="S21" s="32" cm="1">
-        <f t="array" ref="S21:V24">TRANSPOSE(R9:U12)</f>
+        <f t="array" ref="S21:V21">TRANSPOSE(R9:R12)</f>
         <v>1</v>
       </c>
       <c r="T21" s="32">
@@ -8881,7 +11603,7 @@
         <v>0.91708753212843208</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="13.5" customHeight="1">
+    <row r="22" spans="1:23" ht="13.6" customHeight="1">
       <c r="A22" s="23" t="s">
         <v>95</v>
       </c>
@@ -8921,29 +11643,32 @@
       <c r="N22" s="29">
         <v>78.900000000000006</v>
       </c>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="35" t="s">
+      <c r="P22" s="37"/>
+      <c r="Q22" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="R22" s="35"/>
+      <c r="R22" s="46"/>
       <c r="S22" s="32">
         <v>1</v>
       </c>
       <c r="T22" s="32">
-        <v>0.52398753542355847</v>
+        <f>Q5/$P$5</f>
+        <v>0.86997952636757658</v>
       </c>
       <c r="U22" s="32">
-        <v>0.4095629494981427</v>
+        <f t="shared" ref="U22:W22" si="2">R5/$P$5</f>
+        <v>0.90072027403562671</v>
       </c>
       <c r="V22" s="32">
-        <v>0.271820584615732</v>
+        <f t="shared" si="2"/>
+        <v>0.78830135568996362</v>
       </c>
       <c r="W22" s="32">
-        <f t="shared" ref="W22:W24" si="0">(1-V22)*0.85+V22</f>
-        <v>0.89077308769235974</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" ht="13.5" customHeight="1">
+        <f t="shared" si="2"/>
+        <v>0.80177651947337769</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="13.6" customHeight="1">
       <c r="A23" s="23" t="s">
         <v>94</v>
       </c>
@@ -8983,12 +11708,13 @@
       <c r="N23" s="29">
         <v>94.275260000000003</v>
       </c>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="35" t="s">
+      <c r="P23" s="37"/>
+      <c r="Q23" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="R23" s="35"/>
-      <c r="S23" s="32">
+      <c r="R23" s="46"/>
+      <c r="S23" s="32" cm="1">
+        <f t="array" ref="S23:V24">TRANSPOSE(T9:U12)</f>
         <v>1</v>
       </c>
       <c r="T23" s="32">
@@ -9001,11 +11727,11 @@
         <v>0.28182418952618454</v>
       </c>
       <c r="W23" s="32">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="W23:W24" si="3">(1-V23)*0.85+V23</f>
         <v>0.89227362842892766</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="13.5" customHeight="1">
+    <row r="24" spans="1:23" ht="13.6" customHeight="1">
       <c r="A24" s="23" t="s">
         <v>93</v>
       </c>
@@ -9045,11 +11771,11 @@
       <c r="N24" s="29">
         <v>116.386674</v>
       </c>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="35" t="s">
+      <c r="P24" s="37"/>
+      <c r="Q24" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="R24" s="35"/>
+      <c r="R24" s="46"/>
       <c r="S24" s="32">
         <v>1</v>
       </c>
@@ -9063,11 +11789,11 @@
         <v>0.33435852747947475</v>
       </c>
       <c r="W24" s="32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0.90015377912192118</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="13.5" customHeight="1">
+    <row r="25" spans="1:23" ht="13.6" customHeight="1">
       <c r="A25" s="23">
         <v>2008</v>
       </c>
@@ -9107,16 +11833,16 @@
       <c r="N25" s="29">
         <v>119.602272</v>
       </c>
-      <c r="Q25" s="34" t="s">
+      <c r="Q25" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="R25" s="34"/>
-      <c r="S25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-    </row>
-    <row r="26" spans="1:23" ht="13.5" customHeight="1">
+      <c r="R25" s="47"/>
+      <c r="S25" s="47"/>
+      <c r="T25" s="47"/>
+      <c r="U25" s="47"/>
+      <c r="V25" s="47"/>
+    </row>
+    <row r="26" spans="1:23" ht="13.6" customHeight="1">
       <c r="A26" s="23">
         <v>2009</v>
       </c>
@@ -9169,7 +11895,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="13.5" customHeight="1">
+    <row r="27" spans="1:23" ht="13.6" customHeight="1">
       <c r="A27" s="23">
         <v>2010</v>
       </c>
@@ -9209,10 +11935,10 @@
       <c r="N27" s="29">
         <v>178.89815999999999</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q27" s="46" t="s">
         <v>115</v>
       </c>
-      <c r="R27" s="35"/>
+      <c r="R27" s="46"/>
       <c r="S27" s="32" cm="1">
         <f t="array" ref="S27:V30">TRANSPOSE(R13:U16)</f>
         <v>1</v>
@@ -9227,7 +11953,7 @@
         <v>1.1909664551163859</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="13.5" customHeight="1">
+    <row r="28" spans="1:23" ht="13.6" customHeight="1">
       <c r="A28" s="23">
         <v>2011</v>
       </c>
@@ -9267,10 +11993,10 @@
       <c r="N28" s="29">
         <v>173.91</v>
       </c>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="46" t="s">
         <v>114</v>
       </c>
-      <c r="R28" s="35"/>
+      <c r="R28" s="46"/>
       <c r="S28" s="32">
         <v>1</v>
       </c>
@@ -9284,7 +12010,7 @@
         <v>1.1579848729944922</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="13.5" customHeight="1">
+    <row r="29" spans="1:23" ht="13.6" customHeight="1">
       <c r="A29" s="23">
         <v>2012</v>
       </c>
@@ -9324,10 +12050,10 @@
       <c r="N29" s="29">
         <v>163.88936200000001</v>
       </c>
-      <c r="Q29" s="35" t="s">
+      <c r="Q29" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="R29" s="35"/>
+      <c r="R29" s="46"/>
       <c r="S29" s="32">
         <v>1</v>
       </c>
@@ -9341,7 +12067,7 @@
         <v>1.1639053398207673</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="13.5" customHeight="1">
+    <row r="30" spans="1:23" ht="13.6" customHeight="1">
       <c r="A30" s="23">
         <v>2013</v>
       </c>
@@ -9381,10 +12107,10 @@
       <c r="N30" s="29">
         <v>170.29181</v>
       </c>
-      <c r="Q30" s="35" t="s">
+      <c r="Q30" s="46" t="s">
         <v>112</v>
       </c>
-      <c r="R30" s="35"/>
+      <c r="R30" s="46"/>
       <c r="S30" s="32">
         <v>1</v>
       </c>
@@ -9398,7 +12124,7 @@
         <v>0.96542553191489366</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="13.5" customHeight="1">
+    <row r="31" spans="1:23" ht="13.6" customHeight="1">
       <c r="A31" s="23">
         <v>2014</v>
       </c>
@@ -9439,7 +12165,7 @@
         <v>187.771491</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="13.5" customHeight="1">
+    <row r="32" spans="1:23" ht="13.6" customHeight="1">
       <c r="A32" s="23">
         <v>2015</v>
       </c>
@@ -9480,7 +12206,7 @@
         <v>208.06829999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="13.5" customHeight="1">
+    <row r="33" spans="1:14" ht="13.6" customHeight="1">
       <c r="A33" s="23">
         <v>2016</v>
       </c>
@@ -9521,7 +12247,7 @@
         <v>222.44933700000001</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="13.5" customHeight="1">
+    <row r="34" spans="1:14" ht="13.6" customHeight="1">
       <c r="A34" s="23">
         <v>2017</v>
       </c>
@@ -9562,7 +12288,7 @@
         <v>243.55229499999999</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="13.5" customHeight="1">
+    <row r="35" spans="1:14" ht="13.6" customHeight="1">
       <c r="A35" s="23">
         <v>2018</v>
       </c>
@@ -9604,7 +12330,7 @@
         <v>262.49910699999998</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="13.5" customHeight="1">
+    <row r="36" spans="1:14" ht="13.6" customHeight="1">
       <c r="A36" s="24">
         <v>2019</v>
       </c>
@@ -9648,7 +12374,7 @@
         <v>263.2</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="13.5" customHeight="1">
+    <row r="37" spans="1:14" ht="13.6" customHeight="1">
       <c r="A37" s="24">
         <v>2020</v>
       </c>
@@ -9692,7 +12418,7 @@
         <v>240.2</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="13.5" customHeight="1">
+    <row r="38" spans="1:14" ht="13.6" customHeight="1">
       <c r="A38" s="24">
         <v>2021</v>
       </c>
@@ -9736,7 +12462,7 @@
         <v>278.16000000000003</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="13.5" customHeight="1">
+    <row r="39" spans="1:14" ht="13.6" customHeight="1">
       <c r="A39" s="24">
         <v>2022</v>
       </c>
@@ -9777,7 +12503,7 @@
         <v>254.1</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="13.5" customHeight="1">
+    <row r="40" spans="1:14" ht="13.6" customHeight="1">
       <c r="A40" s="20"/>
       <c r="B40" s="21"/>
       <c r="C40" s="21"/>
@@ -9792,7 +12518,7 @@
       <c r="M40" s="21"/>
       <c r="N40" s="20"/>
     </row>
-    <row r="41" spans="1:14" ht="13.5" customHeight="1">
+    <row r="41" spans="1:14" ht="13.6" customHeight="1">
       <c r="A41" s="19"/>
       <c r="C41" s="19"/>
       <c r="E41" s="19"/>
@@ -9801,7 +12527,7 @@
       <c r="J41" s="19"/>
       <c r="L41" s="19"/>
     </row>
-    <row r="42" spans="1:14" ht="13.5" customHeight="1">
+    <row r="42" spans="1:14" ht="13.6" customHeight="1">
       <c r="A42" s="19"/>
       <c r="B42" t="s">
         <v>92</v>
@@ -9813,7 +12539,7 @@
       <c r="J42" s="19"/>
       <c r="L42" s="19"/>
     </row>
-    <row r="43" spans="1:14" ht="13.5" customHeight="1">
+    <row r="43" spans="1:14" ht="13.6" customHeight="1">
       <c r="A43" s="19"/>
       <c r="B43" t="s">
         <v>91</v>
@@ -9837,7 +12563,7 @@
       <c r="J43" s="19"/>
       <c r="L43" s="19"/>
     </row>
-    <row r="44" spans="1:14" ht="13.5" customHeight="1">
+    <row r="44" spans="1:14" ht="13.6" customHeight="1">
       <c r="A44" s="19"/>
       <c r="B44" t="s">
         <v>84</v>
@@ -9861,7 +12587,7 @@
       <c r="J44" s="19"/>
       <c r="L44" s="19"/>
     </row>
-    <row r="45" spans="1:14" ht="13.5" customHeight="1">
+    <row r="45" spans="1:14" ht="13.6" customHeight="1">
       <c r="A45" s="19"/>
       <c r="B45" t="s">
         <v>83</v>
@@ -9885,16 +12611,18 @@
       <c r="J45" s="19"/>
       <c r="L45" s="19"/>
     </row>
-    <row r="46" spans="1:14" ht="13.5" customHeight="1">
+    <row r="46" spans="1:14" ht="13.6" customHeight="1">
       <c r="A46" s="19"/>
       <c r="C46" s="19"/>
       <c r="E46" s="19"/>
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
       <c r="J46" s="19"/>
-      <c r="L46" s="19"/>
-    </row>
-    <row r="47" spans="1:14" ht="13.5" customHeight="1">
+      <c r="L46" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="13.6" customHeight="1">
       <c r="A47" s="19"/>
       <c r="B47" t="s">
         <v>87</v>
@@ -9908,7 +12636,7 @@
       <c r="J47" s="19"/>
       <c r="L47" s="19"/>
     </row>
-    <row r="48" spans="1:14" ht="13.5" customHeight="1">
+    <row r="48" spans="1:14" ht="13.6" customHeight="1">
       <c r="A48" s="19"/>
       <c r="B48" t="s">
         <v>84</v>
@@ -9926,7 +12654,7 @@
       </c>
       <c r="G48" s="19"/>
     </row>
-    <row r="49" spans="2:6" ht="13.5" customHeight="1">
+    <row r="49" spans="2:6" ht="13.6" customHeight="1">
       <c r="B49" t="s">
         <v>83</v>
       </c>
@@ -9942,7 +12670,7 @@
         <v>89979679.590000004</v>
       </c>
     </row>
-    <row r="51" spans="2:6" ht="13.5" customHeight="1">
+    <row r="51" spans="2:6" ht="13.6" customHeight="1">
       <c r="B51" t="s">
         <v>86</v>
       </c>
@@ -9950,7 +12678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="2:6" ht="13.5" customHeight="1">
+    <row r="52" spans="2:6" ht="13.6" customHeight="1">
       <c r="B52" t="s">
         <v>84</v>
       </c>
@@ -9966,7 +12694,7 @@
         <v>0.21888727151535026</v>
       </c>
     </row>
-    <row r="53" spans="2:6" ht="13.5" customHeight="1">
+    <row r="53" spans="2:6" ht="13.6" customHeight="1">
       <c r="B53" t="s">
         <v>83</v>
       </c>
@@ -9984,16 +12712,17 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q25:V25"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="P9:P12"/>
+    <mergeCell ref="P6:U6"/>
+    <mergeCell ref="P7:Q8"/>
+    <mergeCell ref="P13:P16"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="N2:N3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="J2:J3"/>
@@ -10005,17 +12734,16 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="P9:P12"/>
-    <mergeCell ref="P6:U6"/>
-    <mergeCell ref="P7:Q8"/>
-    <mergeCell ref="P13:P16"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Q19:V19"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q25:V25"/>
   </mergeCells>
   <phoneticPr fontId="42" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10033,15 +12761,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100BD1DE36A36CC7845A4126EF01914151E" ma:contentTypeVersion="14" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="310835f059701aa681930bc3a1715053">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="2e2398b5-f60e-4ca0-a4ba-6048b5e4e90c" xmlns:ns3="a06c533b-533a-4f75-b7db-110f073002e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ba933288dd05553e9ce0f804d4dc608" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -10275,6 +12994,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3F56819-4DDA-43FB-95AC-4A54822EFF7A}">
   <ds:schemaRefs>
@@ -10294,14 +13022,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E582446-72E7-41AC-B806-D74F68911B8C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE52FE69-6D5E-4B98-8743-EF2FB207525C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -10319,4 +13039,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E582446-72E7-41AC-B806-D74F68911B8C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>